--- a/paper/human_annotation/annotation_rater2.xlsx
+++ b/paper/human_annotation/annotation_rater2.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -489,31 +489,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>3) other_aspects_you_notice -&gt; optional: list any aspect clearly present that is NOT the one asked.</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4) notes -&gt; optional.</t>
+          <t>Judge only from the review text. You are NOT shown the intended label; that is deliberate.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Judge only from the review text. You are NOT shown the intended label; that is deliberate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Use the dropdowns in columns D and E. Work top to bottom; the order is shuffled for you.</t>
         </is>
@@ -530,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G611"/>
+  <dimension ref="A1:E611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -538,8 +524,6 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,16 +552,6 @@
           <t>sentiment_if_present</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>other_aspects_you_notice</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -597,8 +571,6 @@
       </c>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="3" t="inlineStr"/>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -618,8 +590,6 @@
       </c>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -639,8 +609,6 @@
       </c>
       <c r="D4" s="3" t="inlineStr"/>
       <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -660,8 +628,6 @@
       </c>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -681,8 +647,6 @@
       </c>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -702,8 +666,6 @@
       </c>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -723,8 +685,6 @@
       </c>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -744,8 +704,6 @@
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -765,8 +723,6 @@
       </c>
       <c r="D10" s="3" t="inlineStr"/>
       <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -786,8 +742,6 @@
       </c>
       <c r="D11" s="3" t="inlineStr"/>
       <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -807,8 +761,6 @@
       </c>
       <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -828,8 +780,6 @@
       </c>
       <c r="D13" s="3" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -849,8 +799,6 @@
       </c>
       <c r="D14" s="3" t="inlineStr"/>
       <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -870,8 +818,6 @@
       </c>
       <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -891,8 +837,6 @@
       </c>
       <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -912,8 +856,6 @@
       </c>
       <c r="D17" s="3" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -933,8 +875,6 @@
       </c>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -954,8 +894,6 @@
       </c>
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -975,8 +913,6 @@
       </c>
       <c r="D20" s="3" t="inlineStr"/>
       <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -996,8 +932,6 @@
       </c>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1017,8 +951,6 @@
       </c>
       <c r="D22" s="3" t="inlineStr"/>
       <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -1038,8 +970,6 @@
       </c>
       <c r="D23" s="3" t="inlineStr"/>
       <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -1059,8 +989,6 @@
       </c>
       <c r="D24" s="3" t="inlineStr"/>
       <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -1080,8 +1008,6 @@
       </c>
       <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1101,8 +1027,6 @@
       </c>
       <c r="D26" s="3" t="inlineStr"/>
       <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1122,8 +1046,6 @@
       </c>
       <c r="D27" s="3" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1143,8 +1065,6 @@
       </c>
       <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -1164,8 +1084,6 @@
       </c>
       <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1185,8 +1103,6 @@
       </c>
       <c r="D30" s="3" t="inlineStr"/>
       <c r="E30" s="3" t="inlineStr"/>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1206,8 +1122,6 @@
       </c>
       <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -1227,8 +1141,6 @@
       </c>
       <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -1248,8 +1160,6 @@
       </c>
       <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -1269,8 +1179,6 @@
       </c>
       <c r="D34" s="3" t="inlineStr"/>
       <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1290,8 +1198,6 @@
       </c>
       <c r="D35" s="3" t="inlineStr"/>
       <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1311,8 +1217,6 @@
       </c>
       <c r="D36" s="3" t="inlineStr"/>
       <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1332,8 +1236,6 @@
       </c>
       <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -1353,8 +1255,6 @@
       </c>
       <c r="D38" s="3" t="inlineStr"/>
       <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -1374,8 +1274,6 @@
       </c>
       <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1395,8 +1293,6 @@
       </c>
       <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1416,8 +1312,6 @@
       </c>
       <c r="D41" s="3" t="inlineStr"/>
       <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1437,8 +1331,6 @@
       </c>
       <c r="D42" s="3" t="inlineStr"/>
       <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
-      <c r="G42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1458,8 +1350,6 @@
       </c>
       <c r="D43" s="3" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1479,8 +1369,6 @@
       </c>
       <c r="D44" s="3" t="inlineStr"/>
       <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1500,8 +1388,6 @@
       </c>
       <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1521,8 +1407,6 @@
       </c>
       <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="3" t="inlineStr"/>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1542,8 +1426,6 @@
       </c>
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1563,8 +1445,6 @@
       </c>
       <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1584,8 +1464,6 @@
       </c>
       <c r="D49" s="3" t="inlineStr"/>
       <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -1605,8 +1483,6 @@
       </c>
       <c r="D50" s="3" t="inlineStr"/>
       <c r="E50" s="3" t="inlineStr"/>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -1626,8 +1502,6 @@
       </c>
       <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -1647,8 +1521,6 @@
       </c>
       <c r="D52" s="3" t="inlineStr"/>
       <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -1668,8 +1540,6 @@
       </c>
       <c r="D53" s="3" t="inlineStr"/>
       <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
-      <c r="G53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1689,8 +1559,6 @@
       </c>
       <c r="D54" s="3" t="inlineStr"/>
       <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -1710,8 +1578,6 @@
       </c>
       <c r="D55" s="3" t="inlineStr"/>
       <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -1731,8 +1597,6 @@
       </c>
       <c r="D56" s="3" t="inlineStr"/>
       <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -1752,8 +1616,6 @@
       </c>
       <c r="D57" s="3" t="inlineStr"/>
       <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -1773,8 +1635,6 @@
       </c>
       <c r="D58" s="3" t="inlineStr"/>
       <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -1794,8 +1654,6 @@
       </c>
       <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -1815,8 +1673,6 @@
       </c>
       <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -1836,8 +1692,6 @@
       </c>
       <c r="D61" s="3" t="inlineStr"/>
       <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -1857,8 +1711,6 @@
       </c>
       <c r="D62" s="3" t="inlineStr"/>
       <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -1878,8 +1730,6 @@
       </c>
       <c r="D63" s="3" t="inlineStr"/>
       <c r="E63" s="3" t="inlineStr"/>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -1899,8 +1749,6 @@
       </c>
       <c r="D64" s="3" t="inlineStr"/>
       <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1920,8 +1768,6 @@
       </c>
       <c r="D65" s="3" t="inlineStr"/>
       <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr"/>
-      <c r="G65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -1941,8 +1787,6 @@
       </c>
       <c r="D66" s="3" t="inlineStr"/>
       <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -1962,8 +1806,6 @@
       </c>
       <c r="D67" s="3" t="inlineStr"/>
       <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
-      <c r="G67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -1983,8 +1825,6 @@
       </c>
       <c r="D68" s="3" t="inlineStr"/>
       <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="3" t="inlineStr"/>
-      <c r="G68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -2004,8 +1844,6 @@
       </c>
       <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" s="3" t="inlineStr"/>
-      <c r="G69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -2025,8 +1863,6 @@
       </c>
       <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" s="3" t="inlineStr"/>
-      <c r="F70" s="3" t="inlineStr"/>
-      <c r="G70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -2046,8 +1882,6 @@
       </c>
       <c r="D71" s="3" t="inlineStr"/>
       <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -2067,8 +1901,6 @@
       </c>
       <c r="D72" s="3" t="inlineStr"/>
       <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" s="3" t="inlineStr"/>
-      <c r="G72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -2088,8 +1920,6 @@
       </c>
       <c r="D73" s="3" t="inlineStr"/>
       <c r="E73" s="3" t="inlineStr"/>
-      <c r="F73" s="3" t="inlineStr"/>
-      <c r="G73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
@@ -2109,8 +1939,6 @@
       </c>
       <c r="D74" s="3" t="inlineStr"/>
       <c r="E74" s="3" t="inlineStr"/>
-      <c r="F74" s="3" t="inlineStr"/>
-      <c r="G74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -2130,8 +1958,6 @@
       </c>
       <c r="D75" s="3" t="inlineStr"/>
       <c r="E75" s="3" t="inlineStr"/>
-      <c r="F75" s="3" t="inlineStr"/>
-      <c r="G75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -2151,8 +1977,6 @@
       </c>
       <c r="D76" s="3" t="inlineStr"/>
       <c r="E76" s="3" t="inlineStr"/>
-      <c r="F76" s="3" t="inlineStr"/>
-      <c r="G76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -2172,8 +1996,6 @@
       </c>
       <c r="D77" s="3" t="inlineStr"/>
       <c r="E77" s="3" t="inlineStr"/>
-      <c r="F77" s="3" t="inlineStr"/>
-      <c r="G77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -2193,8 +2015,6 @@
       </c>
       <c r="D78" s="3" t="inlineStr"/>
       <c r="E78" s="3" t="inlineStr"/>
-      <c r="F78" s="3" t="inlineStr"/>
-      <c r="G78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -2214,8 +2034,6 @@
       </c>
       <c r="D79" s="3" t="inlineStr"/>
       <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" s="3" t="inlineStr"/>
-      <c r="G79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
@@ -2235,8 +2053,6 @@
       </c>
       <c r="D80" s="3" t="inlineStr"/>
       <c r="E80" s="3" t="inlineStr"/>
-      <c r="F80" s="3" t="inlineStr"/>
-      <c r="G80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
@@ -2256,8 +2072,6 @@
       </c>
       <c r="D81" s="3" t="inlineStr"/>
       <c r="E81" s="3" t="inlineStr"/>
-      <c r="F81" s="3" t="inlineStr"/>
-      <c r="G81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2277,8 +2091,6 @@
       </c>
       <c r="D82" s="3" t="inlineStr"/>
       <c r="E82" s="3" t="inlineStr"/>
-      <c r="F82" s="3" t="inlineStr"/>
-      <c r="G82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2298,8 +2110,6 @@
       </c>
       <c r="D83" s="3" t="inlineStr"/>
       <c r="E83" s="3" t="inlineStr"/>
-      <c r="F83" s="3" t="inlineStr"/>
-      <c r="G83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -2319,8 +2129,6 @@
       </c>
       <c r="D84" s="3" t="inlineStr"/>
       <c r="E84" s="3" t="inlineStr"/>
-      <c r="F84" s="3" t="inlineStr"/>
-      <c r="G84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -2340,8 +2148,6 @@
       </c>
       <c r="D85" s="3" t="inlineStr"/>
       <c r="E85" s="3" t="inlineStr"/>
-      <c r="F85" s="3" t="inlineStr"/>
-      <c r="G85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -2361,8 +2167,6 @@
       </c>
       <c r="D86" s="3" t="inlineStr"/>
       <c r="E86" s="3" t="inlineStr"/>
-      <c r="F86" s="3" t="inlineStr"/>
-      <c r="G86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2382,8 +2186,6 @@
       </c>
       <c r="D87" s="3" t="inlineStr"/>
       <c r="E87" s="3" t="inlineStr"/>
-      <c r="F87" s="3" t="inlineStr"/>
-      <c r="G87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -2403,8 +2205,6 @@
       </c>
       <c r="D88" s="3" t="inlineStr"/>
       <c r="E88" s="3" t="inlineStr"/>
-      <c r="F88" s="3" t="inlineStr"/>
-      <c r="G88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2424,8 +2224,6 @@
       </c>
       <c r="D89" s="3" t="inlineStr"/>
       <c r="E89" s="3" t="inlineStr"/>
-      <c r="F89" s="3" t="inlineStr"/>
-      <c r="G89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
@@ -2445,8 +2243,6 @@
       </c>
       <c r="D90" s="3" t="inlineStr"/>
       <c r="E90" s="3" t="inlineStr"/>
-      <c r="F90" s="3" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -2466,8 +2262,6 @@
       </c>
       <c r="D91" s="3" t="inlineStr"/>
       <c r="E91" s="3" t="inlineStr"/>
-      <c r="F91" s="3" t="inlineStr"/>
-      <c r="G91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -2487,8 +2281,6 @@
       </c>
       <c r="D92" s="3" t="inlineStr"/>
       <c r="E92" s="3" t="inlineStr"/>
-      <c r="F92" s="3" t="inlineStr"/>
-      <c r="G92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2508,8 +2300,6 @@
       </c>
       <c r="D93" s="3" t="inlineStr"/>
       <c r="E93" s="3" t="inlineStr"/>
-      <c r="F93" s="3" t="inlineStr"/>
-      <c r="G93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -2529,8 +2319,6 @@
       </c>
       <c r="D94" s="3" t="inlineStr"/>
       <c r="E94" s="3" t="inlineStr"/>
-      <c r="F94" s="3" t="inlineStr"/>
-      <c r="G94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -2550,8 +2338,6 @@
       </c>
       <c r="D95" s="3" t="inlineStr"/>
       <c r="E95" s="3" t="inlineStr"/>
-      <c r="F95" s="3" t="inlineStr"/>
-      <c r="G95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -2571,8 +2357,6 @@
       </c>
       <c r="D96" s="3" t="inlineStr"/>
       <c r="E96" s="3" t="inlineStr"/>
-      <c r="F96" s="3" t="inlineStr"/>
-      <c r="G96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -2592,8 +2376,6 @@
       </c>
       <c r="D97" s="3" t="inlineStr"/>
       <c r="E97" s="3" t="inlineStr"/>
-      <c r="F97" s="3" t="inlineStr"/>
-      <c r="G97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -2613,8 +2395,6 @@
       </c>
       <c r="D98" s="3" t="inlineStr"/>
       <c r="E98" s="3" t="inlineStr"/>
-      <c r="F98" s="3" t="inlineStr"/>
-      <c r="G98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -2634,8 +2414,6 @@
       </c>
       <c r="D99" s="3" t="inlineStr"/>
       <c r="E99" s="3" t="inlineStr"/>
-      <c r="F99" s="3" t="inlineStr"/>
-      <c r="G99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -2655,8 +2433,6 @@
       </c>
       <c r="D100" s="3" t="inlineStr"/>
       <c r="E100" s="3" t="inlineStr"/>
-      <c r="F100" s="3" t="inlineStr"/>
-      <c r="G100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
@@ -2676,8 +2452,6 @@
       </c>
       <c r="D101" s="3" t="inlineStr"/>
       <c r="E101" s="3" t="inlineStr"/>
-      <c r="F101" s="3" t="inlineStr"/>
-      <c r="G101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -2697,8 +2471,6 @@
       </c>
       <c r="D102" s="3" t="inlineStr"/>
       <c r="E102" s="3" t="inlineStr"/>
-      <c r="F102" s="3" t="inlineStr"/>
-      <c r="G102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -2718,8 +2490,6 @@
       </c>
       <c r="D103" s="3" t="inlineStr"/>
       <c r="E103" s="3" t="inlineStr"/>
-      <c r="F103" s="3" t="inlineStr"/>
-      <c r="G103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -2739,8 +2509,6 @@
       </c>
       <c r="D104" s="3" t="inlineStr"/>
       <c r="E104" s="3" t="inlineStr"/>
-      <c r="F104" s="3" t="inlineStr"/>
-      <c r="G104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
@@ -2760,8 +2528,6 @@
       </c>
       <c r="D105" s="3" t="inlineStr"/>
       <c r="E105" s="3" t="inlineStr"/>
-      <c r="F105" s="3" t="inlineStr"/>
-      <c r="G105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -2781,8 +2547,6 @@
       </c>
       <c r="D106" s="3" t="inlineStr"/>
       <c r="E106" s="3" t="inlineStr"/>
-      <c r="F106" s="3" t="inlineStr"/>
-      <c r="G106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
@@ -2802,8 +2566,6 @@
       </c>
       <c r="D107" s="3" t="inlineStr"/>
       <c r="E107" s="3" t="inlineStr"/>
-      <c r="F107" s="3" t="inlineStr"/>
-      <c r="G107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -2823,8 +2585,6 @@
       </c>
       <c r="D108" s="3" t="inlineStr"/>
       <c r="E108" s="3" t="inlineStr"/>
-      <c r="F108" s="3" t="inlineStr"/>
-      <c r="G108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
@@ -2844,8 +2604,6 @@
       </c>
       <c r="D109" s="3" t="inlineStr"/>
       <c r="E109" s="3" t="inlineStr"/>
-      <c r="F109" s="3" t="inlineStr"/>
-      <c r="G109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -2865,8 +2623,6 @@
       </c>
       <c r="D110" s="3" t="inlineStr"/>
       <c r="E110" s="3" t="inlineStr"/>
-      <c r="F110" s="3" t="inlineStr"/>
-      <c r="G110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -2886,8 +2642,6 @@
       </c>
       <c r="D111" s="3" t="inlineStr"/>
       <c r="E111" s="3" t="inlineStr"/>
-      <c r="F111" s="3" t="inlineStr"/>
-      <c r="G111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -2907,8 +2661,6 @@
       </c>
       <c r="D112" s="3" t="inlineStr"/>
       <c r="E112" s="3" t="inlineStr"/>
-      <c r="F112" s="3" t="inlineStr"/>
-      <c r="G112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -2928,8 +2680,6 @@
       </c>
       <c r="D113" s="3" t="inlineStr"/>
       <c r="E113" s="3" t="inlineStr"/>
-      <c r="F113" s="3" t="inlineStr"/>
-      <c r="G113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -2949,8 +2699,6 @@
       </c>
       <c r="D114" s="3" t="inlineStr"/>
       <c r="E114" s="3" t="inlineStr"/>
-      <c r="F114" s="3" t="inlineStr"/>
-      <c r="G114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -2970,8 +2718,6 @@
       </c>
       <c r="D115" s="3" t="inlineStr"/>
       <c r="E115" s="3" t="inlineStr"/>
-      <c r="F115" s="3" t="inlineStr"/>
-      <c r="G115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -2991,8 +2737,6 @@
       </c>
       <c r="D116" s="3" t="inlineStr"/>
       <c r="E116" s="3" t="inlineStr"/>
-      <c r="F116" s="3" t="inlineStr"/>
-      <c r="G116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
@@ -3012,8 +2756,6 @@
       </c>
       <c r="D117" s="3" t="inlineStr"/>
       <c r="E117" s="3" t="inlineStr"/>
-      <c r="F117" s="3" t="inlineStr"/>
-      <c r="G117" s="3" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -3033,8 +2775,6 @@
       </c>
       <c r="D118" s="3" t="inlineStr"/>
       <c r="E118" s="3" t="inlineStr"/>
-      <c r="F118" s="3" t="inlineStr"/>
-      <c r="G118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
@@ -3054,8 +2794,6 @@
       </c>
       <c r="D119" s="3" t="inlineStr"/>
       <c r="E119" s="3" t="inlineStr"/>
-      <c r="F119" s="3" t="inlineStr"/>
-      <c r="G119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -3075,8 +2813,6 @@
       </c>
       <c r="D120" s="3" t="inlineStr"/>
       <c r="E120" s="3" t="inlineStr"/>
-      <c r="F120" s="3" t="inlineStr"/>
-      <c r="G120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
@@ -3096,8 +2832,6 @@
       </c>
       <c r="D121" s="3" t="inlineStr"/>
       <c r="E121" s="3" t="inlineStr"/>
-      <c r="F121" s="3" t="inlineStr"/>
-      <c r="G121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -3117,8 +2851,6 @@
       </c>
       <c r="D122" s="3" t="inlineStr"/>
       <c r="E122" s="3" t="inlineStr"/>
-      <c r="F122" s="3" t="inlineStr"/>
-      <c r="G122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
@@ -3138,8 +2870,6 @@
       </c>
       <c r="D123" s="3" t="inlineStr"/>
       <c r="E123" s="3" t="inlineStr"/>
-      <c r="F123" s="3" t="inlineStr"/>
-      <c r="G123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
@@ -3159,8 +2889,6 @@
       </c>
       <c r="D124" s="3" t="inlineStr"/>
       <c r="E124" s="3" t="inlineStr"/>
-      <c r="F124" s="3" t="inlineStr"/>
-      <c r="G124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
@@ -3180,8 +2908,6 @@
       </c>
       <c r="D125" s="3" t="inlineStr"/>
       <c r="E125" s="3" t="inlineStr"/>
-      <c r="F125" s="3" t="inlineStr"/>
-      <c r="G125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
@@ -3201,8 +2927,6 @@
       </c>
       <c r="D126" s="3" t="inlineStr"/>
       <c r="E126" s="3" t="inlineStr"/>
-      <c r="F126" s="3" t="inlineStr"/>
-      <c r="G126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
@@ -3222,8 +2946,6 @@
       </c>
       <c r="D127" s="3" t="inlineStr"/>
       <c r="E127" s="3" t="inlineStr"/>
-      <c r="F127" s="3" t="inlineStr"/>
-      <c r="G127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
@@ -3243,8 +2965,6 @@
       </c>
       <c r="D128" s="3" t="inlineStr"/>
       <c r="E128" s="3" t="inlineStr"/>
-      <c r="F128" s="3" t="inlineStr"/>
-      <c r="G128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
@@ -3264,8 +2984,6 @@
       </c>
       <c r="D129" s="3" t="inlineStr"/>
       <c r="E129" s="3" t="inlineStr"/>
-      <c r="F129" s="3" t="inlineStr"/>
-      <c r="G129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
@@ -3285,8 +3003,6 @@
       </c>
       <c r="D130" s="3" t="inlineStr"/>
       <c r="E130" s="3" t="inlineStr"/>
-      <c r="F130" s="3" t="inlineStr"/>
-      <c r="G130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
@@ -3306,8 +3022,6 @@
       </c>
       <c r="D131" s="3" t="inlineStr"/>
       <c r="E131" s="3" t="inlineStr"/>
-      <c r="F131" s="3" t="inlineStr"/>
-      <c r="G131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
@@ -3327,8 +3041,6 @@
       </c>
       <c r="D132" s="3" t="inlineStr"/>
       <c r="E132" s="3" t="inlineStr"/>
-      <c r="F132" s="3" t="inlineStr"/>
-      <c r="G132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
@@ -3348,8 +3060,6 @@
       </c>
       <c r="D133" s="3" t="inlineStr"/>
       <c r="E133" s="3" t="inlineStr"/>
-      <c r="F133" s="3" t="inlineStr"/>
-      <c r="G133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
@@ -3369,8 +3079,6 @@
       </c>
       <c r="D134" s="3" t="inlineStr"/>
       <c r="E134" s="3" t="inlineStr"/>
-      <c r="F134" s="3" t="inlineStr"/>
-      <c r="G134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
@@ -3390,8 +3098,6 @@
       </c>
       <c r="D135" s="3" t="inlineStr"/>
       <c r="E135" s="3" t="inlineStr"/>
-      <c r="F135" s="3" t="inlineStr"/>
-      <c r="G135" s="3" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
@@ -3411,8 +3117,6 @@
       </c>
       <c r="D136" s="3" t="inlineStr"/>
       <c r="E136" s="3" t="inlineStr"/>
-      <c r="F136" s="3" t="inlineStr"/>
-      <c r="G136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
@@ -3432,8 +3136,6 @@
       </c>
       <c r="D137" s="3" t="inlineStr"/>
       <c r="E137" s="3" t="inlineStr"/>
-      <c r="F137" s="3" t="inlineStr"/>
-      <c r="G137" s="3" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
@@ -3453,8 +3155,6 @@
       </c>
       <c r="D138" s="3" t="inlineStr"/>
       <c r="E138" s="3" t="inlineStr"/>
-      <c r="F138" s="3" t="inlineStr"/>
-      <c r="G138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
@@ -3474,8 +3174,6 @@
       </c>
       <c r="D139" s="3" t="inlineStr"/>
       <c r="E139" s="3" t="inlineStr"/>
-      <c r="F139" s="3" t="inlineStr"/>
-      <c r="G139" s="3" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
@@ -3495,8 +3193,6 @@
       </c>
       <c r="D140" s="3" t="inlineStr"/>
       <c r="E140" s="3" t="inlineStr"/>
-      <c r="F140" s="3" t="inlineStr"/>
-      <c r="G140" s="3" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
@@ -3516,8 +3212,6 @@
       </c>
       <c r="D141" s="3" t="inlineStr"/>
       <c r="E141" s="3" t="inlineStr"/>
-      <c r="F141" s="3" t="inlineStr"/>
-      <c r="G141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
@@ -3537,8 +3231,6 @@
       </c>
       <c r="D142" s="3" t="inlineStr"/>
       <c r="E142" s="3" t="inlineStr"/>
-      <c r="F142" s="3" t="inlineStr"/>
-      <c r="G142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
@@ -3558,8 +3250,6 @@
       </c>
       <c r="D143" s="3" t="inlineStr"/>
       <c r="E143" s="3" t="inlineStr"/>
-      <c r="F143" s="3" t="inlineStr"/>
-      <c r="G143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
@@ -3579,8 +3269,6 @@
       </c>
       <c r="D144" s="3" t="inlineStr"/>
       <c r="E144" s="3" t="inlineStr"/>
-      <c r="F144" s="3" t="inlineStr"/>
-      <c r="G144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
@@ -3600,8 +3288,6 @@
       </c>
       <c r="D145" s="3" t="inlineStr"/>
       <c r="E145" s="3" t="inlineStr"/>
-      <c r="F145" s="3" t="inlineStr"/>
-      <c r="G145" s="3" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
@@ -3621,8 +3307,6 @@
       </c>
       <c r="D146" s="3" t="inlineStr"/>
       <c r="E146" s="3" t="inlineStr"/>
-      <c r="F146" s="3" t="inlineStr"/>
-      <c r="G146" s="3" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
@@ -3642,8 +3326,6 @@
       </c>
       <c r="D147" s="3" t="inlineStr"/>
       <c r="E147" s="3" t="inlineStr"/>
-      <c r="F147" s="3" t="inlineStr"/>
-      <c r="G147" s="3" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
@@ -3663,8 +3345,6 @@
       </c>
       <c r="D148" s="3" t="inlineStr"/>
       <c r="E148" s="3" t="inlineStr"/>
-      <c r="F148" s="3" t="inlineStr"/>
-      <c r="G148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
@@ -3684,8 +3364,6 @@
       </c>
       <c r="D149" s="3" t="inlineStr"/>
       <c r="E149" s="3" t="inlineStr"/>
-      <c r="F149" s="3" t="inlineStr"/>
-      <c r="G149" s="3" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
@@ -3705,8 +3383,6 @@
       </c>
       <c r="D150" s="3" t="inlineStr"/>
       <c r="E150" s="3" t="inlineStr"/>
-      <c r="F150" s="3" t="inlineStr"/>
-      <c r="G150" s="3" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
@@ -3726,8 +3402,6 @@
       </c>
       <c r="D151" s="3" t="inlineStr"/>
       <c r="E151" s="3" t="inlineStr"/>
-      <c r="F151" s="3" t="inlineStr"/>
-      <c r="G151" s="3" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
@@ -3747,8 +3421,6 @@
       </c>
       <c r="D152" s="3" t="inlineStr"/>
       <c r="E152" s="3" t="inlineStr"/>
-      <c r="F152" s="3" t="inlineStr"/>
-      <c r="G152" s="3" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
@@ -3768,8 +3440,6 @@
       </c>
       <c r="D153" s="3" t="inlineStr"/>
       <c r="E153" s="3" t="inlineStr"/>
-      <c r="F153" s="3" t="inlineStr"/>
-      <c r="G153" s="3" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
@@ -3789,8 +3459,6 @@
       </c>
       <c r="D154" s="3" t="inlineStr"/>
       <c r="E154" s="3" t="inlineStr"/>
-      <c r="F154" s="3" t="inlineStr"/>
-      <c r="G154" s="3" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
@@ -3810,8 +3478,6 @@
       </c>
       <c r="D155" s="3" t="inlineStr"/>
       <c r="E155" s="3" t="inlineStr"/>
-      <c r="F155" s="3" t="inlineStr"/>
-      <c r="G155" s="3" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
@@ -3831,8 +3497,6 @@
       </c>
       <c r="D156" s="3" t="inlineStr"/>
       <c r="E156" s="3" t="inlineStr"/>
-      <c r="F156" s="3" t="inlineStr"/>
-      <c r="G156" s="3" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
@@ -3852,8 +3516,6 @@
       </c>
       <c r="D157" s="3" t="inlineStr"/>
       <c r="E157" s="3" t="inlineStr"/>
-      <c r="F157" s="3" t="inlineStr"/>
-      <c r="G157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
@@ -3873,8 +3535,6 @@
       </c>
       <c r="D158" s="3" t="inlineStr"/>
       <c r="E158" s="3" t="inlineStr"/>
-      <c r="F158" s="3" t="inlineStr"/>
-      <c r="G158" s="3" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -3894,8 +3554,6 @@
       </c>
       <c r="D159" s="3" t="inlineStr"/>
       <c r="E159" s="3" t="inlineStr"/>
-      <c r="F159" s="3" t="inlineStr"/>
-      <c r="G159" s="3" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -3915,8 +3573,6 @@
       </c>
       <c r="D160" s="3" t="inlineStr"/>
       <c r="E160" s="3" t="inlineStr"/>
-      <c r="F160" s="3" t="inlineStr"/>
-      <c r="G160" s="3" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -3936,8 +3592,6 @@
       </c>
       <c r="D161" s="3" t="inlineStr"/>
       <c r="E161" s="3" t="inlineStr"/>
-      <c r="F161" s="3" t="inlineStr"/>
-      <c r="G161" s="3" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
@@ -3957,8 +3611,6 @@
       </c>
       <c r="D162" s="3" t="inlineStr"/>
       <c r="E162" s="3" t="inlineStr"/>
-      <c r="F162" s="3" t="inlineStr"/>
-      <c r="G162" s="3" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
@@ -3978,8 +3630,6 @@
       </c>
       <c r="D163" s="3" t="inlineStr"/>
       <c r="E163" s="3" t="inlineStr"/>
-      <c r="F163" s="3" t="inlineStr"/>
-      <c r="G163" s="3" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
@@ -3999,8 +3649,6 @@
       </c>
       <c r="D164" s="3" t="inlineStr"/>
       <c r="E164" s="3" t="inlineStr"/>
-      <c r="F164" s="3" t="inlineStr"/>
-      <c r="G164" s="3" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
@@ -4020,8 +3668,6 @@
       </c>
       <c r="D165" s="3" t="inlineStr"/>
       <c r="E165" s="3" t="inlineStr"/>
-      <c r="F165" s="3" t="inlineStr"/>
-      <c r="G165" s="3" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
@@ -4041,8 +3687,6 @@
       </c>
       <c r="D166" s="3" t="inlineStr"/>
       <c r="E166" s="3" t="inlineStr"/>
-      <c r="F166" s="3" t="inlineStr"/>
-      <c r="G166" s="3" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
@@ -4062,8 +3706,6 @@
       </c>
       <c r="D167" s="3" t="inlineStr"/>
       <c r="E167" s="3" t="inlineStr"/>
-      <c r="F167" s="3" t="inlineStr"/>
-      <c r="G167" s="3" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
@@ -4083,8 +3725,6 @@
       </c>
       <c r="D168" s="3" t="inlineStr"/>
       <c r="E168" s="3" t="inlineStr"/>
-      <c r="F168" s="3" t="inlineStr"/>
-      <c r="G168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
@@ -4104,8 +3744,6 @@
       </c>
       <c r="D169" s="3" t="inlineStr"/>
       <c r="E169" s="3" t="inlineStr"/>
-      <c r="F169" s="3" t="inlineStr"/>
-      <c r="G169" s="3" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
@@ -4125,8 +3763,6 @@
       </c>
       <c r="D170" s="3" t="inlineStr"/>
       <c r="E170" s="3" t="inlineStr"/>
-      <c r="F170" s="3" t="inlineStr"/>
-      <c r="G170" s="3" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
@@ -4146,8 +3782,6 @@
       </c>
       <c r="D171" s="3" t="inlineStr"/>
       <c r="E171" s="3" t="inlineStr"/>
-      <c r="F171" s="3" t="inlineStr"/>
-      <c r="G171" s="3" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
@@ -4167,8 +3801,6 @@
       </c>
       <c r="D172" s="3" t="inlineStr"/>
       <c r="E172" s="3" t="inlineStr"/>
-      <c r="F172" s="3" t="inlineStr"/>
-      <c r="G172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
@@ -4188,8 +3820,6 @@
       </c>
       <c r="D173" s="3" t="inlineStr"/>
       <c r="E173" s="3" t="inlineStr"/>
-      <c r="F173" s="3" t="inlineStr"/>
-      <c r="G173" s="3" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
@@ -4209,8 +3839,6 @@
       </c>
       <c r="D174" s="3" t="inlineStr"/>
       <c r="E174" s="3" t="inlineStr"/>
-      <c r="F174" s="3" t="inlineStr"/>
-      <c r="G174" s="3" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
@@ -4230,8 +3858,6 @@
       </c>
       <c r="D175" s="3" t="inlineStr"/>
       <c r="E175" s="3" t="inlineStr"/>
-      <c r="F175" s="3" t="inlineStr"/>
-      <c r="G175" s="3" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
@@ -4251,8 +3877,6 @@
       </c>
       <c r="D176" s="3" t="inlineStr"/>
       <c r="E176" s="3" t="inlineStr"/>
-      <c r="F176" s="3" t="inlineStr"/>
-      <c r="G176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
@@ -4272,8 +3896,6 @@
       </c>
       <c r="D177" s="3" t="inlineStr"/>
       <c r="E177" s="3" t="inlineStr"/>
-      <c r="F177" s="3" t="inlineStr"/>
-      <c r="G177" s="3" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
@@ -4293,8 +3915,6 @@
       </c>
       <c r="D178" s="3" t="inlineStr"/>
       <c r="E178" s="3" t="inlineStr"/>
-      <c r="F178" s="3" t="inlineStr"/>
-      <c r="G178" s="3" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
@@ -4314,8 +3934,6 @@
       </c>
       <c r="D179" s="3" t="inlineStr"/>
       <c r="E179" s="3" t="inlineStr"/>
-      <c r="F179" s="3" t="inlineStr"/>
-      <c r="G179" s="3" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
@@ -4335,8 +3953,6 @@
       </c>
       <c r="D180" s="3" t="inlineStr"/>
       <c r="E180" s="3" t="inlineStr"/>
-      <c r="F180" s="3" t="inlineStr"/>
-      <c r="G180" s="3" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
@@ -4356,8 +3972,6 @@
       </c>
       <c r="D181" s="3" t="inlineStr"/>
       <c r="E181" s="3" t="inlineStr"/>
-      <c r="F181" s="3" t="inlineStr"/>
-      <c r="G181" s="3" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
@@ -4377,8 +3991,6 @@
       </c>
       <c r="D182" s="3" t="inlineStr"/>
       <c r="E182" s="3" t="inlineStr"/>
-      <c r="F182" s="3" t="inlineStr"/>
-      <c r="G182" s="3" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
@@ -4398,8 +4010,6 @@
       </c>
       <c r="D183" s="3" t="inlineStr"/>
       <c r="E183" s="3" t="inlineStr"/>
-      <c r="F183" s="3" t="inlineStr"/>
-      <c r="G183" s="3" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
@@ -4419,8 +4029,6 @@
       </c>
       <c r="D184" s="3" t="inlineStr"/>
       <c r="E184" s="3" t="inlineStr"/>
-      <c r="F184" s="3" t="inlineStr"/>
-      <c r="G184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
@@ -4440,8 +4048,6 @@
       </c>
       <c r="D185" s="3" t="inlineStr"/>
       <c r="E185" s="3" t="inlineStr"/>
-      <c r="F185" s="3" t="inlineStr"/>
-      <c r="G185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
@@ -4461,8 +4067,6 @@
       </c>
       <c r="D186" s="3" t="inlineStr"/>
       <c r="E186" s="3" t="inlineStr"/>
-      <c r="F186" s="3" t="inlineStr"/>
-      <c r="G186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
@@ -4482,8 +4086,6 @@
       </c>
       <c r="D187" s="3" t="inlineStr"/>
       <c r="E187" s="3" t="inlineStr"/>
-      <c r="F187" s="3" t="inlineStr"/>
-      <c r="G187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
@@ -4503,8 +4105,6 @@
       </c>
       <c r="D188" s="3" t="inlineStr"/>
       <c r="E188" s="3" t="inlineStr"/>
-      <c r="F188" s="3" t="inlineStr"/>
-      <c r="G188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
@@ -4524,8 +4124,6 @@
       </c>
       <c r="D189" s="3" t="inlineStr"/>
       <c r="E189" s="3" t="inlineStr"/>
-      <c r="F189" s="3" t="inlineStr"/>
-      <c r="G189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
@@ -4545,8 +4143,6 @@
       </c>
       <c r="D190" s="3" t="inlineStr"/>
       <c r="E190" s="3" t="inlineStr"/>
-      <c r="F190" s="3" t="inlineStr"/>
-      <c r="G190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
@@ -4566,8 +4162,6 @@
       </c>
       <c r="D191" s="3" t="inlineStr"/>
       <c r="E191" s="3" t="inlineStr"/>
-      <c r="F191" s="3" t="inlineStr"/>
-      <c r="G191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
@@ -4587,8 +4181,6 @@
       </c>
       <c r="D192" s="3" t="inlineStr"/>
       <c r="E192" s="3" t="inlineStr"/>
-      <c r="F192" s="3" t="inlineStr"/>
-      <c r="G192" s="3" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
@@ -4608,8 +4200,6 @@
       </c>
       <c r="D193" s="3" t="inlineStr"/>
       <c r="E193" s="3" t="inlineStr"/>
-      <c r="F193" s="3" t="inlineStr"/>
-      <c r="G193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -4629,8 +4219,6 @@
       </c>
       <c r="D194" s="3" t="inlineStr"/>
       <c r="E194" s="3" t="inlineStr"/>
-      <c r="F194" s="3" t="inlineStr"/>
-      <c r="G194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -4650,8 +4238,6 @@
       </c>
       <c r="D195" s="3" t="inlineStr"/>
       <c r="E195" s="3" t="inlineStr"/>
-      <c r="F195" s="3" t="inlineStr"/>
-      <c r="G195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -4671,8 +4257,6 @@
       </c>
       <c r="D196" s="3" t="inlineStr"/>
       <c r="E196" s="3" t="inlineStr"/>
-      <c r="F196" s="3" t="inlineStr"/>
-      <c r="G196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -4692,8 +4276,6 @@
       </c>
       <c r="D197" s="3" t="inlineStr"/>
       <c r="E197" s="3" t="inlineStr"/>
-      <c r="F197" s="3" t="inlineStr"/>
-      <c r="G197" s="3" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
@@ -4713,8 +4295,6 @@
       </c>
       <c r="D198" s="3" t="inlineStr"/>
       <c r="E198" s="3" t="inlineStr"/>
-      <c r="F198" s="3" t="inlineStr"/>
-      <c r="G198" s="3" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
@@ -4734,8 +4314,6 @@
       </c>
       <c r="D199" s="3" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr"/>
-      <c r="F199" s="3" t="inlineStr"/>
-      <c r="G199" s="3" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
@@ -4755,8 +4333,6 @@
       </c>
       <c r="D200" s="3" t="inlineStr"/>
       <c r="E200" s="3" t="inlineStr"/>
-      <c r="F200" s="3" t="inlineStr"/>
-      <c r="G200" s="3" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
@@ -4776,8 +4352,6 @@
       </c>
       <c r="D201" s="3" t="inlineStr"/>
       <c r="E201" s="3" t="inlineStr"/>
-      <c r="F201" s="3" t="inlineStr"/>
-      <c r="G201" s="3" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
@@ -4797,8 +4371,6 @@
       </c>
       <c r="D202" s="3" t="inlineStr"/>
       <c r="E202" s="3" t="inlineStr"/>
-      <c r="F202" s="3" t="inlineStr"/>
-      <c r="G202" s="3" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
@@ -4818,8 +4390,6 @@
       </c>
       <c r="D203" s="3" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr"/>
-      <c r="F203" s="3" t="inlineStr"/>
-      <c r="G203" s="3" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
@@ -4839,8 +4409,6 @@
       </c>
       <c r="D204" s="3" t="inlineStr"/>
       <c r="E204" s="3" t="inlineStr"/>
-      <c r="F204" s="3" t="inlineStr"/>
-      <c r="G204" s="3" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
@@ -4860,8 +4428,6 @@
       </c>
       <c r="D205" s="3" t="inlineStr"/>
       <c r="E205" s="3" t="inlineStr"/>
-      <c r="F205" s="3" t="inlineStr"/>
-      <c r="G205" s="3" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
@@ -4881,8 +4447,6 @@
       </c>
       <c r="D206" s="3" t="inlineStr"/>
       <c r="E206" s="3" t="inlineStr"/>
-      <c r="F206" s="3" t="inlineStr"/>
-      <c r="G206" s="3" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
@@ -4902,8 +4466,6 @@
       </c>
       <c r="D207" s="3" t="inlineStr"/>
       <c r="E207" s="3" t="inlineStr"/>
-      <c r="F207" s="3" t="inlineStr"/>
-      <c r="G207" s="3" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
@@ -4923,8 +4485,6 @@
       </c>
       <c r="D208" s="3" t="inlineStr"/>
       <c r="E208" s="3" t="inlineStr"/>
-      <c r="F208" s="3" t="inlineStr"/>
-      <c r="G208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
@@ -4944,8 +4504,6 @@
       </c>
       <c r="D209" s="3" t="inlineStr"/>
       <c r="E209" s="3" t="inlineStr"/>
-      <c r="F209" s="3" t="inlineStr"/>
-      <c r="G209" s="3" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
@@ -4965,8 +4523,6 @@
       </c>
       <c r="D210" s="3" t="inlineStr"/>
       <c r="E210" s="3" t="inlineStr"/>
-      <c r="F210" s="3" t="inlineStr"/>
-      <c r="G210" s="3" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
@@ -4986,8 +4542,6 @@
       </c>
       <c r="D211" s="3" t="inlineStr"/>
       <c r="E211" s="3" t="inlineStr"/>
-      <c r="F211" s="3" t="inlineStr"/>
-      <c r="G211" s="3" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
@@ -5007,8 +4561,6 @@
       </c>
       <c r="D212" s="3" t="inlineStr"/>
       <c r="E212" s="3" t="inlineStr"/>
-      <c r="F212" s="3" t="inlineStr"/>
-      <c r="G212" s="3" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
@@ -5028,8 +4580,6 @@
       </c>
       <c r="D213" s="3" t="inlineStr"/>
       <c r="E213" s="3" t="inlineStr"/>
-      <c r="F213" s="3" t="inlineStr"/>
-      <c r="G213" s="3" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
@@ -5049,8 +4599,6 @@
       </c>
       <c r="D214" s="3" t="inlineStr"/>
       <c r="E214" s="3" t="inlineStr"/>
-      <c r="F214" s="3" t="inlineStr"/>
-      <c r="G214" s="3" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
@@ -5070,8 +4618,6 @@
       </c>
       <c r="D215" s="3" t="inlineStr"/>
       <c r="E215" s="3" t="inlineStr"/>
-      <c r="F215" s="3" t="inlineStr"/>
-      <c r="G215" s="3" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -5091,8 +4637,6 @@
       </c>
       <c r="D216" s="3" t="inlineStr"/>
       <c r="E216" s="3" t="inlineStr"/>
-      <c r="F216" s="3" t="inlineStr"/>
-      <c r="G216" s="3" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -5112,8 +4656,6 @@
       </c>
       <c r="D217" s="3" t="inlineStr"/>
       <c r="E217" s="3" t="inlineStr"/>
-      <c r="F217" s="3" t="inlineStr"/>
-      <c r="G217" s="3" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
@@ -5133,8 +4675,6 @@
       </c>
       <c r="D218" s="3" t="inlineStr"/>
       <c r="E218" s="3" t="inlineStr"/>
-      <c r="F218" s="3" t="inlineStr"/>
-      <c r="G218" s="3" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -5154,8 +4694,6 @@
       </c>
       <c r="D219" s="3" t="inlineStr"/>
       <c r="E219" s="3" t="inlineStr"/>
-      <c r="F219" s="3" t="inlineStr"/>
-      <c r="G219" s="3" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -5175,8 +4713,6 @@
       </c>
       <c r="D220" s="3" t="inlineStr"/>
       <c r="E220" s="3" t="inlineStr"/>
-      <c r="F220" s="3" t="inlineStr"/>
-      <c r="G220" s="3" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -5196,8 +4732,6 @@
       </c>
       <c r="D221" s="3" t="inlineStr"/>
       <c r="E221" s="3" t="inlineStr"/>
-      <c r="F221" s="3" t="inlineStr"/>
-      <c r="G221" s="3" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -5217,8 +4751,6 @@
       </c>
       <c r="D222" s="3" t="inlineStr"/>
       <c r="E222" s="3" t="inlineStr"/>
-      <c r="F222" s="3" t="inlineStr"/>
-      <c r="G222" s="3" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -5238,8 +4770,6 @@
       </c>
       <c r="D223" s="3" t="inlineStr"/>
       <c r="E223" s="3" t="inlineStr"/>
-      <c r="F223" s="3" t="inlineStr"/>
-      <c r="G223" s="3" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
@@ -5259,8 +4789,6 @@
       </c>
       <c r="D224" s="3" t="inlineStr"/>
       <c r="E224" s="3" t="inlineStr"/>
-      <c r="F224" s="3" t="inlineStr"/>
-      <c r="G224" s="3" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
@@ -5280,8 +4808,6 @@
       </c>
       <c r="D225" s="3" t="inlineStr"/>
       <c r="E225" s="3" t="inlineStr"/>
-      <c r="F225" s="3" t="inlineStr"/>
-      <c r="G225" s="3" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -5301,8 +4827,6 @@
       </c>
       <c r="D226" s="3" t="inlineStr"/>
       <c r="E226" s="3" t="inlineStr"/>
-      <c r="F226" s="3" t="inlineStr"/>
-      <c r="G226" s="3" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -5322,8 +4846,6 @@
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr"/>
-      <c r="F227" s="3" t="inlineStr"/>
-      <c r="G227" s="3" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -5343,8 +4865,6 @@
       </c>
       <c r="D228" s="3" t="inlineStr"/>
       <c r="E228" s="3" t="inlineStr"/>
-      <c r="F228" s="3" t="inlineStr"/>
-      <c r="G228" s="3" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -5364,8 +4884,6 @@
       </c>
       <c r="D229" s="3" t="inlineStr"/>
       <c r="E229" s="3" t="inlineStr"/>
-      <c r="F229" s="3" t="inlineStr"/>
-      <c r="G229" s="3" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -5385,8 +4903,6 @@
       </c>
       <c r="D230" s="3" t="inlineStr"/>
       <c r="E230" s="3" t="inlineStr"/>
-      <c r="F230" s="3" t="inlineStr"/>
-      <c r="G230" s="3" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
@@ -5406,8 +4922,6 @@
       </c>
       <c r="D231" s="3" t="inlineStr"/>
       <c r="E231" s="3" t="inlineStr"/>
-      <c r="F231" s="3" t="inlineStr"/>
-      <c r="G231" s="3" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
@@ -5427,8 +4941,6 @@
       </c>
       <c r="D232" s="3" t="inlineStr"/>
       <c r="E232" s="3" t="inlineStr"/>
-      <c r="F232" s="3" t="inlineStr"/>
-      <c r="G232" s="3" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -5448,8 +4960,6 @@
       </c>
       <c r="D233" s="3" t="inlineStr"/>
       <c r="E233" s="3" t="inlineStr"/>
-      <c r="F233" s="3" t="inlineStr"/>
-      <c r="G233" s="3" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -5469,8 +4979,6 @@
       </c>
       <c r="D234" s="3" t="inlineStr"/>
       <c r="E234" s="3" t="inlineStr"/>
-      <c r="F234" s="3" t="inlineStr"/>
-      <c r="G234" s="3" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -5490,8 +4998,6 @@
       </c>
       <c r="D235" s="3" t="inlineStr"/>
       <c r="E235" s="3" t="inlineStr"/>
-      <c r="F235" s="3" t="inlineStr"/>
-      <c r="G235" s="3" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -5511,8 +5017,6 @@
       </c>
       <c r="D236" s="3" t="inlineStr"/>
       <c r="E236" s="3" t="inlineStr"/>
-      <c r="F236" s="3" t="inlineStr"/>
-      <c r="G236" s="3" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -5532,8 +5036,6 @@
       </c>
       <c r="D237" s="3" t="inlineStr"/>
       <c r="E237" s="3" t="inlineStr"/>
-      <c r="F237" s="3" t="inlineStr"/>
-      <c r="G237" s="3" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
@@ -5553,8 +5055,6 @@
       </c>
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr"/>
-      <c r="F238" s="3" t="inlineStr"/>
-      <c r="G238" s="3" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
@@ -5574,8 +5074,6 @@
       </c>
       <c r="D239" s="3" t="inlineStr"/>
       <c r="E239" s="3" t="inlineStr"/>
-      <c r="F239" s="3" t="inlineStr"/>
-      <c r="G239" s="3" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -5595,8 +5093,6 @@
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr"/>
-      <c r="F240" s="3" t="inlineStr"/>
-      <c r="G240" s="3" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -5616,8 +5112,6 @@
       </c>
       <c r="D241" s="3" t="inlineStr"/>
       <c r="E241" s="3" t="inlineStr"/>
-      <c r="F241" s="3" t="inlineStr"/>
-      <c r="G241" s="3" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -5637,8 +5131,6 @@
       </c>
       <c r="D242" s="3" t="inlineStr"/>
       <c r="E242" s="3" t="inlineStr"/>
-      <c r="F242" s="3" t="inlineStr"/>
-      <c r="G242" s="3" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -5658,8 +5150,6 @@
       </c>
       <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr"/>
-      <c r="F243" s="3" t="inlineStr"/>
-      <c r="G243" s="3" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -5679,8 +5169,6 @@
       </c>
       <c r="D244" s="3" t="inlineStr"/>
       <c r="E244" s="3" t="inlineStr"/>
-      <c r="F244" s="3" t="inlineStr"/>
-      <c r="G244" s="3" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
@@ -5700,8 +5188,6 @@
       </c>
       <c r="D245" s="3" t="inlineStr"/>
       <c r="E245" s="3" t="inlineStr"/>
-      <c r="F245" s="3" t="inlineStr"/>
-      <c r="G245" s="3" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
@@ -5721,8 +5207,6 @@
       </c>
       <c r="D246" s="3" t="inlineStr"/>
       <c r="E246" s="3" t="inlineStr"/>
-      <c r="F246" s="3" t="inlineStr"/>
-      <c r="G246" s="3" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -5742,8 +5226,6 @@
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr"/>
-      <c r="F247" s="3" t="inlineStr"/>
-      <c r="G247" s="3" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -5763,8 +5245,6 @@
       </c>
       <c r="D248" s="3" t="inlineStr"/>
       <c r="E248" s="3" t="inlineStr"/>
-      <c r="F248" s="3" t="inlineStr"/>
-      <c r="G248" s="3" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
@@ -5784,8 +5264,6 @@
       </c>
       <c r="D249" s="3" t="inlineStr"/>
       <c r="E249" s="3" t="inlineStr"/>
-      <c r="F249" s="3" t="inlineStr"/>
-      <c r="G249" s="3" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
@@ -5805,8 +5283,6 @@
       </c>
       <c r="D250" s="3" t="inlineStr"/>
       <c r="E250" s="3" t="inlineStr"/>
-      <c r="F250" s="3" t="inlineStr"/>
-      <c r="G250" s="3" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -5826,8 +5302,6 @@
       </c>
       <c r="D251" s="3" t="inlineStr"/>
       <c r="E251" s="3" t="inlineStr"/>
-      <c r="F251" s="3" t="inlineStr"/>
-      <c r="G251" s="3" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
@@ -5847,8 +5321,6 @@
       </c>
       <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr"/>
-      <c r="F252" s="3" t="inlineStr"/>
-      <c r="G252" s="3" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
@@ -5868,8 +5340,6 @@
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr"/>
-      <c r="F253" s="3" t="inlineStr"/>
-      <c r="G253" s="3" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
@@ -5889,8 +5359,6 @@
       </c>
       <c r="D254" s="3" t="inlineStr"/>
       <c r="E254" s="3" t="inlineStr"/>
-      <c r="F254" s="3" t="inlineStr"/>
-      <c r="G254" s="3" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -5910,8 +5378,6 @@
       </c>
       <c r="D255" s="3" t="inlineStr"/>
       <c r="E255" s="3" t="inlineStr"/>
-      <c r="F255" s="3" t="inlineStr"/>
-      <c r="G255" s="3" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
@@ -5931,8 +5397,6 @@
       </c>
       <c r="D256" s="3" t="inlineStr"/>
       <c r="E256" s="3" t="inlineStr"/>
-      <c r="F256" s="3" t="inlineStr"/>
-      <c r="G256" s="3" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -5952,8 +5416,6 @@
       </c>
       <c r="D257" s="3" t="inlineStr"/>
       <c r="E257" s="3" t="inlineStr"/>
-      <c r="F257" s="3" t="inlineStr"/>
-      <c r="G257" s="3" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
@@ -5973,8 +5435,6 @@
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr"/>
-      <c r="F258" s="3" t="inlineStr"/>
-      <c r="G258" s="3" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -5994,8 +5454,6 @@
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr"/>
-      <c r="F259" s="3" t="inlineStr"/>
-      <c r="G259" s="3" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
@@ -6015,8 +5473,6 @@
       </c>
       <c r="D260" s="3" t="inlineStr"/>
       <c r="E260" s="3" t="inlineStr"/>
-      <c r="F260" s="3" t="inlineStr"/>
-      <c r="G260" s="3" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -6036,8 +5492,6 @@
       </c>
       <c r="D261" s="3" t="inlineStr"/>
       <c r="E261" s="3" t="inlineStr"/>
-      <c r="F261" s="3" t="inlineStr"/>
-      <c r="G261" s="3" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -6057,8 +5511,6 @@
       </c>
       <c r="D262" s="3" t="inlineStr"/>
       <c r="E262" s="3" t="inlineStr"/>
-      <c r="F262" s="3" t="inlineStr"/>
-      <c r="G262" s="3" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -6078,8 +5530,6 @@
       </c>
       <c r="D263" s="3" t="inlineStr"/>
       <c r="E263" s="3" t="inlineStr"/>
-      <c r="F263" s="3" t="inlineStr"/>
-      <c r="G263" s="3" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
@@ -6099,8 +5549,6 @@
       </c>
       <c r="D264" s="3" t="inlineStr"/>
       <c r="E264" s="3" t="inlineStr"/>
-      <c r="F264" s="3" t="inlineStr"/>
-      <c r="G264" s="3" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -6120,8 +5568,6 @@
       </c>
       <c r="D265" s="3" t="inlineStr"/>
       <c r="E265" s="3" t="inlineStr"/>
-      <c r="F265" s="3" t="inlineStr"/>
-      <c r="G265" s="3" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
@@ -6141,8 +5587,6 @@
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr"/>
-      <c r="F266" s="3" t="inlineStr"/>
-      <c r="G266" s="3" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
@@ -6162,8 +5606,6 @@
       </c>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr"/>
-      <c r="F267" s="3" t="inlineStr"/>
-      <c r="G267" s="3" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -6183,8 +5625,6 @@
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr"/>
-      <c r="F268" s="3" t="inlineStr"/>
-      <c r="G268" s="3" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -6204,8 +5644,6 @@
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr"/>
-      <c r="F269" s="3" t="inlineStr"/>
-      <c r="G269" s="3" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
@@ -6225,8 +5663,6 @@
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr"/>
-      <c r="F270" s="3" t="inlineStr"/>
-      <c r="G270" s="3" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -6246,8 +5682,6 @@
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr"/>
-      <c r="F271" s="3" t="inlineStr"/>
-      <c r="G271" s="3" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
@@ -6267,8 +5701,6 @@
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr"/>
-      <c r="F272" s="3" t="inlineStr"/>
-      <c r="G272" s="3" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
@@ -6288,8 +5720,6 @@
       </c>
       <c r="D273" s="3" t="inlineStr"/>
       <c r="E273" s="3" t="inlineStr"/>
-      <c r="F273" s="3" t="inlineStr"/>
-      <c r="G273" s="3" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
@@ -6309,8 +5739,6 @@
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr"/>
-      <c r="F274" s="3" t="inlineStr"/>
-      <c r="G274" s="3" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
@@ -6330,8 +5758,6 @@
       </c>
       <c r="D275" s="3" t="inlineStr"/>
       <c r="E275" s="3" t="inlineStr"/>
-      <c r="F275" s="3" t="inlineStr"/>
-      <c r="G275" s="3" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
@@ -6351,8 +5777,6 @@
       </c>
       <c r="D276" s="3" t="inlineStr"/>
       <c r="E276" s="3" t="inlineStr"/>
-      <c r="F276" s="3" t="inlineStr"/>
-      <c r="G276" s="3" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
@@ -6372,8 +5796,6 @@
       </c>
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr"/>
-      <c r="F277" s="3" t="inlineStr"/>
-      <c r="G277" s="3" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
@@ -6393,8 +5815,6 @@
       </c>
       <c r="D278" s="3" t="inlineStr"/>
       <c r="E278" s="3" t="inlineStr"/>
-      <c r="F278" s="3" t="inlineStr"/>
-      <c r="G278" s="3" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
@@ -6414,8 +5834,6 @@
       </c>
       <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr"/>
-      <c r="F279" s="3" t="inlineStr"/>
-      <c r="G279" s="3" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
@@ -6435,8 +5853,6 @@
       </c>
       <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr"/>
-      <c r="F280" s="3" t="inlineStr"/>
-      <c r="G280" s="3" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
@@ -6456,8 +5872,6 @@
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr"/>
-      <c r="F281" s="3" t="inlineStr"/>
-      <c r="G281" s="3" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
@@ -6477,8 +5891,6 @@
       </c>
       <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr"/>
-      <c r="F282" s="3" t="inlineStr"/>
-      <c r="G282" s="3" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
@@ -6498,8 +5910,6 @@
       </c>
       <c r="D283" s="3" t="inlineStr"/>
       <c r="E283" s="3" t="inlineStr"/>
-      <c r="F283" s="3" t="inlineStr"/>
-      <c r="G283" s="3" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
@@ -6519,8 +5929,6 @@
       </c>
       <c r="D284" s="3" t="inlineStr"/>
       <c r="E284" s="3" t="inlineStr"/>
-      <c r="F284" s="3" t="inlineStr"/>
-      <c r="G284" s="3" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
@@ -6540,8 +5948,6 @@
       </c>
       <c r="D285" s="3" t="inlineStr"/>
       <c r="E285" s="3" t="inlineStr"/>
-      <c r="F285" s="3" t="inlineStr"/>
-      <c r="G285" s="3" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
@@ -6561,8 +5967,6 @@
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr"/>
-      <c r="F286" s="3" t="inlineStr"/>
-      <c r="G286" s="3" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
@@ -6582,8 +5986,6 @@
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr"/>
-      <c r="F287" s="3" t="inlineStr"/>
-      <c r="G287" s="3" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
@@ -6603,8 +6005,6 @@
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr"/>
-      <c r="F288" s="3" t="inlineStr"/>
-      <c r="G288" s="3" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
@@ -6624,8 +6024,6 @@
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr"/>
-      <c r="F289" s="3" t="inlineStr"/>
-      <c r="G289" s="3" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="3" t="inlineStr">
@@ -6645,8 +6043,6 @@
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr"/>
-      <c r="F290" s="3" t="inlineStr"/>
-      <c r="G290" s="3" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="3" t="inlineStr">
@@ -6666,8 +6062,6 @@
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr"/>
-      <c r="F291" s="3" t="inlineStr"/>
-      <c r="G291" s="3" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="3" t="inlineStr">
@@ -6687,8 +6081,6 @@
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr"/>
-      <c r="F292" s="3" t="inlineStr"/>
-      <c r="G292" s="3" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="3" t="inlineStr">
@@ -6708,8 +6100,6 @@
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr"/>
-      <c r="F293" s="3" t="inlineStr"/>
-      <c r="G293" s="3" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="3" t="inlineStr">
@@ -6729,8 +6119,6 @@
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr"/>
-      <c r="F294" s="3" t="inlineStr"/>
-      <c r="G294" s="3" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="3" t="inlineStr">
@@ -6750,8 +6138,6 @@
       </c>
       <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr"/>
-      <c r="F295" s="3" t="inlineStr"/>
-      <c r="G295" s="3" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="3" t="inlineStr">
@@ -6771,8 +6157,6 @@
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr"/>
-      <c r="F296" s="3" t="inlineStr"/>
-      <c r="G296" s="3" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -6792,8 +6176,6 @@
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr"/>
-      <c r="F297" s="3" t="inlineStr"/>
-      <c r="G297" s="3" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
@@ -6813,8 +6195,6 @@
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr"/>
-      <c r="F298" s="3" t="inlineStr"/>
-      <c r="G298" s="3" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="3" t="inlineStr">
@@ -6834,8 +6214,6 @@
       </c>
       <c r="D299" s="3" t="inlineStr"/>
       <c r="E299" s="3" t="inlineStr"/>
-      <c r="F299" s="3" t="inlineStr"/>
-      <c r="G299" s="3" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="3" t="inlineStr">
@@ -6855,8 +6233,6 @@
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr"/>
-      <c r="F300" s="3" t="inlineStr"/>
-      <c r="G300" s="3" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="3" t="inlineStr">
@@ -6876,8 +6252,6 @@
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr"/>
-      <c r="F301" s="3" t="inlineStr"/>
-      <c r="G301" s="3" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="3" t="inlineStr">
@@ -6897,8 +6271,6 @@
       </c>
       <c r="D302" s="3" t="inlineStr"/>
       <c r="E302" s="3" t="inlineStr"/>
-      <c r="F302" s="3" t="inlineStr"/>
-      <c r="G302" s="3" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="3" t="inlineStr">
@@ -6918,8 +6290,6 @@
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr"/>
-      <c r="F303" s="3" t="inlineStr"/>
-      <c r="G303" s="3" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="3" t="inlineStr">
@@ -6939,8 +6309,6 @@
       </c>
       <c r="D304" s="3" t="inlineStr"/>
       <c r="E304" s="3" t="inlineStr"/>
-      <c r="F304" s="3" t="inlineStr"/>
-      <c r="G304" s="3" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="3" t="inlineStr">
@@ -6960,8 +6328,6 @@
       </c>
       <c r="D305" s="3" t="inlineStr"/>
       <c r="E305" s="3" t="inlineStr"/>
-      <c r="F305" s="3" t="inlineStr"/>
-      <c r="G305" s="3" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="3" t="inlineStr">
@@ -6981,8 +6347,6 @@
       </c>
       <c r="D306" s="3" t="inlineStr"/>
       <c r="E306" s="3" t="inlineStr"/>
-      <c r="F306" s="3" t="inlineStr"/>
-      <c r="G306" s="3" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -7002,8 +6366,6 @@
       </c>
       <c r="D307" s="3" t="inlineStr"/>
       <c r="E307" s="3" t="inlineStr"/>
-      <c r="F307" s="3" t="inlineStr"/>
-      <c r="G307" s="3" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
@@ -7023,8 +6385,6 @@
       </c>
       <c r="D308" s="3" t="inlineStr"/>
       <c r="E308" s="3" t="inlineStr"/>
-      <c r="F308" s="3" t="inlineStr"/>
-      <c r="G308" s="3" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="3" t="inlineStr">
@@ -7044,8 +6404,6 @@
       </c>
       <c r="D309" s="3" t="inlineStr"/>
       <c r="E309" s="3" t="inlineStr"/>
-      <c r="F309" s="3" t="inlineStr"/>
-      <c r="G309" s="3" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="3" t="inlineStr">
@@ -7065,8 +6423,6 @@
       </c>
       <c r="D310" s="3" t="inlineStr"/>
       <c r="E310" s="3" t="inlineStr"/>
-      <c r="F310" s="3" t="inlineStr"/>
-      <c r="G310" s="3" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="3" t="inlineStr">
@@ -7086,8 +6442,6 @@
       </c>
       <c r="D311" s="3" t="inlineStr"/>
       <c r="E311" s="3" t="inlineStr"/>
-      <c r="F311" s="3" t="inlineStr"/>
-      <c r="G311" s="3" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="3" t="inlineStr">
@@ -7107,8 +6461,6 @@
       </c>
       <c r="D312" s="3" t="inlineStr"/>
       <c r="E312" s="3" t="inlineStr"/>
-      <c r="F312" s="3" t="inlineStr"/>
-      <c r="G312" s="3" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="3" t="inlineStr">
@@ -7128,8 +6480,6 @@
       </c>
       <c r="D313" s="3" t="inlineStr"/>
       <c r="E313" s="3" t="inlineStr"/>
-      <c r="F313" s="3" t="inlineStr"/>
-      <c r="G313" s="3" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
@@ -7149,8 +6499,6 @@
       </c>
       <c r="D314" s="3" t="inlineStr"/>
       <c r="E314" s="3" t="inlineStr"/>
-      <c r="F314" s="3" t="inlineStr"/>
-      <c r="G314" s="3" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
@@ -7170,8 +6518,6 @@
       </c>
       <c r="D315" s="3" t="inlineStr"/>
       <c r="E315" s="3" t="inlineStr"/>
-      <c r="F315" s="3" t="inlineStr"/>
-      <c r="G315" s="3" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="3" t="inlineStr">
@@ -7191,8 +6537,6 @@
       </c>
       <c r="D316" s="3" t="inlineStr"/>
       <c r="E316" s="3" t="inlineStr"/>
-      <c r="F316" s="3" t="inlineStr"/>
-      <c r="G316" s="3" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="3" t="inlineStr">
@@ -7212,8 +6556,6 @@
       </c>
       <c r="D317" s="3" t="inlineStr"/>
       <c r="E317" s="3" t="inlineStr"/>
-      <c r="F317" s="3" t="inlineStr"/>
-      <c r="G317" s="3" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="3" t="inlineStr">
@@ -7233,8 +6575,6 @@
       </c>
       <c r="D318" s="3" t="inlineStr"/>
       <c r="E318" s="3" t="inlineStr"/>
-      <c r="F318" s="3" t="inlineStr"/>
-      <c r="G318" s="3" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="3" t="inlineStr">
@@ -7254,8 +6594,6 @@
       </c>
       <c r="D319" s="3" t="inlineStr"/>
       <c r="E319" s="3" t="inlineStr"/>
-      <c r="F319" s="3" t="inlineStr"/>
-      <c r="G319" s="3" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="3" t="inlineStr">
@@ -7275,8 +6613,6 @@
       </c>
       <c r="D320" s="3" t="inlineStr"/>
       <c r="E320" s="3" t="inlineStr"/>
-      <c r="F320" s="3" t="inlineStr"/>
-      <c r="G320" s="3" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="3" t="inlineStr">
@@ -7296,8 +6632,6 @@
       </c>
       <c r="D321" s="3" t="inlineStr"/>
       <c r="E321" s="3" t="inlineStr"/>
-      <c r="F321" s="3" t="inlineStr"/>
-      <c r="G321" s="3" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="3" t="inlineStr">
@@ -7317,8 +6651,6 @@
       </c>
       <c r="D322" s="3" t="inlineStr"/>
       <c r="E322" s="3" t="inlineStr"/>
-      <c r="F322" s="3" t="inlineStr"/>
-      <c r="G322" s="3" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="3" t="inlineStr">
@@ -7338,8 +6670,6 @@
       </c>
       <c r="D323" s="3" t="inlineStr"/>
       <c r="E323" s="3" t="inlineStr"/>
-      <c r="F323" s="3" t="inlineStr"/>
-      <c r="G323" s="3" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
@@ -7359,8 +6689,6 @@
       </c>
       <c r="D324" s="3" t="inlineStr"/>
       <c r="E324" s="3" t="inlineStr"/>
-      <c r="F324" s="3" t="inlineStr"/>
-      <c r="G324" s="3" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -7380,8 +6708,6 @@
       </c>
       <c r="D325" s="3" t="inlineStr"/>
       <c r="E325" s="3" t="inlineStr"/>
-      <c r="F325" s="3" t="inlineStr"/>
-      <c r="G325" s="3" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="3" t="inlineStr">
@@ -7401,8 +6727,6 @@
       </c>
       <c r="D326" s="3" t="inlineStr"/>
       <c r="E326" s="3" t="inlineStr"/>
-      <c r="F326" s="3" t="inlineStr"/>
-      <c r="G326" s="3" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="3" t="inlineStr">
@@ -7422,8 +6746,6 @@
       </c>
       <c r="D327" s="3" t="inlineStr"/>
       <c r="E327" s="3" t="inlineStr"/>
-      <c r="F327" s="3" t="inlineStr"/>
-      <c r="G327" s="3" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="3" t="inlineStr">
@@ -7443,8 +6765,6 @@
       </c>
       <c r="D328" s="3" t="inlineStr"/>
       <c r="E328" s="3" t="inlineStr"/>
-      <c r="F328" s="3" t="inlineStr"/>
-      <c r="G328" s="3" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="3" t="inlineStr">
@@ -7464,8 +6784,6 @@
       </c>
       <c r="D329" s="3" t="inlineStr"/>
       <c r="E329" s="3" t="inlineStr"/>
-      <c r="F329" s="3" t="inlineStr"/>
-      <c r="G329" s="3" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="3" t="inlineStr">
@@ -7485,8 +6803,6 @@
       </c>
       <c r="D330" s="3" t="inlineStr"/>
       <c r="E330" s="3" t="inlineStr"/>
-      <c r="F330" s="3" t="inlineStr"/>
-      <c r="G330" s="3" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="3" t="inlineStr">
@@ -7506,8 +6822,6 @@
       </c>
       <c r="D331" s="3" t="inlineStr"/>
       <c r="E331" s="3" t="inlineStr"/>
-      <c r="F331" s="3" t="inlineStr"/>
-      <c r="G331" s="3" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="3" t="inlineStr">
@@ -7527,8 +6841,6 @@
       </c>
       <c r="D332" s="3" t="inlineStr"/>
       <c r="E332" s="3" t="inlineStr"/>
-      <c r="F332" s="3" t="inlineStr"/>
-      <c r="G332" s="3" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="3" t="inlineStr">
@@ -7548,8 +6860,6 @@
       </c>
       <c r="D333" s="3" t="inlineStr"/>
       <c r="E333" s="3" t="inlineStr"/>
-      <c r="F333" s="3" t="inlineStr"/>
-      <c r="G333" s="3" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
@@ -7569,8 +6879,6 @@
       </c>
       <c r="D334" s="3" t="inlineStr"/>
       <c r="E334" s="3" t="inlineStr"/>
-      <c r="F334" s="3" t="inlineStr"/>
-      <c r="G334" s="3" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
@@ -7590,8 +6898,6 @@
       </c>
       <c r="D335" s="3" t="inlineStr"/>
       <c r="E335" s="3" t="inlineStr"/>
-      <c r="F335" s="3" t="inlineStr"/>
-      <c r="G335" s="3" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="3" t="inlineStr">
@@ -7611,8 +6917,6 @@
       </c>
       <c r="D336" s="3" t="inlineStr"/>
       <c r="E336" s="3" t="inlineStr"/>
-      <c r="F336" s="3" t="inlineStr"/>
-      <c r="G336" s="3" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="3" t="inlineStr">
@@ -7632,8 +6936,6 @@
       </c>
       <c r="D337" s="3" t="inlineStr"/>
       <c r="E337" s="3" t="inlineStr"/>
-      <c r="F337" s="3" t="inlineStr"/>
-      <c r="G337" s="3" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="3" t="inlineStr">
@@ -7653,8 +6955,6 @@
       </c>
       <c r="D338" s="3" t="inlineStr"/>
       <c r="E338" s="3" t="inlineStr"/>
-      <c r="F338" s="3" t="inlineStr"/>
-      <c r="G338" s="3" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="3" t="inlineStr">
@@ -7674,8 +6974,6 @@
       </c>
       <c r="D339" s="3" t="inlineStr"/>
       <c r="E339" s="3" t="inlineStr"/>
-      <c r="F339" s="3" t="inlineStr"/>
-      <c r="G339" s="3" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="3" t="inlineStr">
@@ -7695,8 +6993,6 @@
       </c>
       <c r="D340" s="3" t="inlineStr"/>
       <c r="E340" s="3" t="inlineStr"/>
-      <c r="F340" s="3" t="inlineStr"/>
-      <c r="G340" s="3" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="3" t="inlineStr">
@@ -7716,8 +7012,6 @@
       </c>
       <c r="D341" s="3" t="inlineStr"/>
       <c r="E341" s="3" t="inlineStr"/>
-      <c r="F341" s="3" t="inlineStr"/>
-      <c r="G341" s="3" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="3" t="inlineStr">
@@ -7737,8 +7031,6 @@
       </c>
       <c r="D342" s="3" t="inlineStr"/>
       <c r="E342" s="3" t="inlineStr"/>
-      <c r="F342" s="3" t="inlineStr"/>
-      <c r="G342" s="3" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="3" t="inlineStr">
@@ -7758,8 +7050,6 @@
       </c>
       <c r="D343" s="3" t="inlineStr"/>
       <c r="E343" s="3" t="inlineStr"/>
-      <c r="F343" s="3" t="inlineStr"/>
-      <c r="G343" s="3" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
@@ -7779,8 +7069,6 @@
       </c>
       <c r="D344" s="3" t="inlineStr"/>
       <c r="E344" s="3" t="inlineStr"/>
-      <c r="F344" s="3" t="inlineStr"/>
-      <c r="G344" s="3" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
@@ -7800,8 +7088,6 @@
       </c>
       <c r="D345" s="3" t="inlineStr"/>
       <c r="E345" s="3" t="inlineStr"/>
-      <c r="F345" s="3" t="inlineStr"/>
-      <c r="G345" s="3" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="3" t="inlineStr">
@@ -7821,8 +7107,6 @@
       </c>
       <c r="D346" s="3" t="inlineStr"/>
       <c r="E346" s="3" t="inlineStr"/>
-      <c r="F346" s="3" t="inlineStr"/>
-      <c r="G346" s="3" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="3" t="inlineStr">
@@ -7842,8 +7126,6 @@
       </c>
       <c r="D347" s="3" t="inlineStr"/>
       <c r="E347" s="3" t="inlineStr"/>
-      <c r="F347" s="3" t="inlineStr"/>
-      <c r="G347" s="3" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="3" t="inlineStr">
@@ -7863,8 +7145,6 @@
       </c>
       <c r="D348" s="3" t="inlineStr"/>
       <c r="E348" s="3" t="inlineStr"/>
-      <c r="F348" s="3" t="inlineStr"/>
-      <c r="G348" s="3" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="3" t="inlineStr">
@@ -7884,8 +7164,6 @@
       </c>
       <c r="D349" s="3" t="inlineStr"/>
       <c r="E349" s="3" t="inlineStr"/>
-      <c r="F349" s="3" t="inlineStr"/>
-      <c r="G349" s="3" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="3" t="inlineStr">
@@ -7905,8 +7183,6 @@
       </c>
       <c r="D350" s="3" t="inlineStr"/>
       <c r="E350" s="3" t="inlineStr"/>
-      <c r="F350" s="3" t="inlineStr"/>
-      <c r="G350" s="3" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
@@ -7926,8 +7202,6 @@
       </c>
       <c r="D351" s="3" t="inlineStr"/>
       <c r="E351" s="3" t="inlineStr"/>
-      <c r="F351" s="3" t="inlineStr"/>
-      <c r="G351" s="3" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
@@ -7947,8 +7221,6 @@
       </c>
       <c r="D352" s="3" t="inlineStr"/>
       <c r="E352" s="3" t="inlineStr"/>
-      <c r="F352" s="3" t="inlineStr"/>
-      <c r="G352" s="3" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="3" t="inlineStr">
@@ -7968,8 +7240,6 @@
       </c>
       <c r="D353" s="3" t="inlineStr"/>
       <c r="E353" s="3" t="inlineStr"/>
-      <c r="F353" s="3" t="inlineStr"/>
-      <c r="G353" s="3" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="3" t="inlineStr">
@@ -7989,8 +7259,6 @@
       </c>
       <c r="D354" s="3" t="inlineStr"/>
       <c r="E354" s="3" t="inlineStr"/>
-      <c r="F354" s="3" t="inlineStr"/>
-      <c r="G354" s="3" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="3" t="inlineStr">
@@ -8010,8 +7278,6 @@
       </c>
       <c r="D355" s="3" t="inlineStr"/>
       <c r="E355" s="3" t="inlineStr"/>
-      <c r="F355" s="3" t="inlineStr"/>
-      <c r="G355" s="3" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="3" t="inlineStr">
@@ -8031,8 +7297,6 @@
       </c>
       <c r="D356" s="3" t="inlineStr"/>
       <c r="E356" s="3" t="inlineStr"/>
-      <c r="F356" s="3" t="inlineStr"/>
-      <c r="G356" s="3" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="3" t="inlineStr">
@@ -8052,8 +7316,6 @@
       </c>
       <c r="D357" s="3" t="inlineStr"/>
       <c r="E357" s="3" t="inlineStr"/>
-      <c r="F357" s="3" t="inlineStr"/>
-      <c r="G357" s="3" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="3" t="inlineStr">
@@ -8073,8 +7335,6 @@
       </c>
       <c r="D358" s="3" t="inlineStr"/>
       <c r="E358" s="3" t="inlineStr"/>
-      <c r="F358" s="3" t="inlineStr"/>
-      <c r="G358" s="3" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="3" t="inlineStr">
@@ -8094,8 +7354,6 @@
       </c>
       <c r="D359" s="3" t="inlineStr"/>
       <c r="E359" s="3" t="inlineStr"/>
-      <c r="F359" s="3" t="inlineStr"/>
-      <c r="G359" s="3" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="3" t="inlineStr">
@@ -8115,8 +7373,6 @@
       </c>
       <c r="D360" s="3" t="inlineStr"/>
       <c r="E360" s="3" t="inlineStr"/>
-      <c r="F360" s="3" t="inlineStr"/>
-      <c r="G360" s="3" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
@@ -8136,8 +7392,6 @@
       </c>
       <c r="D361" s="3" t="inlineStr"/>
       <c r="E361" s="3" t="inlineStr"/>
-      <c r="F361" s="3" t="inlineStr"/>
-      <c r="G361" s="3" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
@@ -8157,8 +7411,6 @@
       </c>
       <c r="D362" s="3" t="inlineStr"/>
       <c r="E362" s="3" t="inlineStr"/>
-      <c r="F362" s="3" t="inlineStr"/>
-      <c r="G362" s="3" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="3" t="inlineStr">
@@ -8178,8 +7430,6 @@
       </c>
       <c r="D363" s="3" t="inlineStr"/>
       <c r="E363" s="3" t="inlineStr"/>
-      <c r="F363" s="3" t="inlineStr"/>
-      <c r="G363" s="3" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="3" t="inlineStr">
@@ -8199,8 +7449,6 @@
       </c>
       <c r="D364" s="3" t="inlineStr"/>
       <c r="E364" s="3" t="inlineStr"/>
-      <c r="F364" s="3" t="inlineStr"/>
-      <c r="G364" s="3" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="3" t="inlineStr">
@@ -8220,8 +7468,6 @@
       </c>
       <c r="D365" s="3" t="inlineStr"/>
       <c r="E365" s="3" t="inlineStr"/>
-      <c r="F365" s="3" t="inlineStr"/>
-      <c r="G365" s="3" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="3" t="inlineStr">
@@ -8241,8 +7487,6 @@
       </c>
       <c r="D366" s="3" t="inlineStr"/>
       <c r="E366" s="3" t="inlineStr"/>
-      <c r="F366" s="3" t="inlineStr"/>
-      <c r="G366" s="3" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="3" t="inlineStr">
@@ -8262,8 +7506,6 @@
       </c>
       <c r="D367" s="3" t="inlineStr"/>
       <c r="E367" s="3" t="inlineStr"/>
-      <c r="F367" s="3" t="inlineStr"/>
-      <c r="G367" s="3" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="3" t="inlineStr">
@@ -8283,8 +7525,6 @@
       </c>
       <c r="D368" s="3" t="inlineStr"/>
       <c r="E368" s="3" t="inlineStr"/>
-      <c r="F368" s="3" t="inlineStr"/>
-      <c r="G368" s="3" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="3" t="inlineStr">
@@ -8304,8 +7544,6 @@
       </c>
       <c r="D369" s="3" t="inlineStr"/>
       <c r="E369" s="3" t="inlineStr"/>
-      <c r="F369" s="3" t="inlineStr"/>
-      <c r="G369" s="3" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="3" t="inlineStr">
@@ -8325,8 +7563,6 @@
       </c>
       <c r="D370" s="3" t="inlineStr"/>
       <c r="E370" s="3" t="inlineStr"/>
-      <c r="F370" s="3" t="inlineStr"/>
-      <c r="G370" s="3" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
@@ -8346,8 +7582,6 @@
       </c>
       <c r="D371" s="3" t="inlineStr"/>
       <c r="E371" s="3" t="inlineStr"/>
-      <c r="F371" s="3" t="inlineStr"/>
-      <c r="G371" s="3" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
@@ -8367,8 +7601,6 @@
       </c>
       <c r="D372" s="3" t="inlineStr"/>
       <c r="E372" s="3" t="inlineStr"/>
-      <c r="F372" s="3" t="inlineStr"/>
-      <c r="G372" s="3" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="3" t="inlineStr">
@@ -8388,8 +7620,6 @@
       </c>
       <c r="D373" s="3" t="inlineStr"/>
       <c r="E373" s="3" t="inlineStr"/>
-      <c r="F373" s="3" t="inlineStr"/>
-      <c r="G373" s="3" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="3" t="inlineStr">
@@ -8409,8 +7639,6 @@
       </c>
       <c r="D374" s="3" t="inlineStr"/>
       <c r="E374" s="3" t="inlineStr"/>
-      <c r="F374" s="3" t="inlineStr"/>
-      <c r="G374" s="3" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="3" t="inlineStr">
@@ -8430,8 +7658,6 @@
       </c>
       <c r="D375" s="3" t="inlineStr"/>
       <c r="E375" s="3" t="inlineStr"/>
-      <c r="F375" s="3" t="inlineStr"/>
-      <c r="G375" s="3" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="3" t="inlineStr">
@@ -8451,8 +7677,6 @@
       </c>
       <c r="D376" s="3" t="inlineStr"/>
       <c r="E376" s="3" t="inlineStr"/>
-      <c r="F376" s="3" t="inlineStr"/>
-      <c r="G376" s="3" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="3" t="inlineStr">
@@ -8472,8 +7696,6 @@
       </c>
       <c r="D377" s="3" t="inlineStr"/>
       <c r="E377" s="3" t="inlineStr"/>
-      <c r="F377" s="3" t="inlineStr"/>
-      <c r="G377" s="3" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="3" t="inlineStr">
@@ -8493,8 +7715,6 @@
       </c>
       <c r="D378" s="3" t="inlineStr"/>
       <c r="E378" s="3" t="inlineStr"/>
-      <c r="F378" s="3" t="inlineStr"/>
-      <c r="G378" s="3" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="3" t="inlineStr">
@@ -8514,8 +7734,6 @@
       </c>
       <c r="D379" s="3" t="inlineStr"/>
       <c r="E379" s="3" t="inlineStr"/>
-      <c r="F379" s="3" t="inlineStr"/>
-      <c r="G379" s="3" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="3" t="inlineStr">
@@ -8535,8 +7753,6 @@
       </c>
       <c r="D380" s="3" t="inlineStr"/>
       <c r="E380" s="3" t="inlineStr"/>
-      <c r="F380" s="3" t="inlineStr"/>
-      <c r="G380" s="3" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
@@ -8556,8 +7772,6 @@
       </c>
       <c r="D381" s="3" t="inlineStr"/>
       <c r="E381" s="3" t="inlineStr"/>
-      <c r="F381" s="3" t="inlineStr"/>
-      <c r="G381" s="3" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
@@ -8577,8 +7791,6 @@
       </c>
       <c r="D382" s="3" t="inlineStr"/>
       <c r="E382" s="3" t="inlineStr"/>
-      <c r="F382" s="3" t="inlineStr"/>
-      <c r="G382" s="3" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="3" t="inlineStr">
@@ -8598,8 +7810,6 @@
       </c>
       <c r="D383" s="3" t="inlineStr"/>
       <c r="E383" s="3" t="inlineStr"/>
-      <c r="F383" s="3" t="inlineStr"/>
-      <c r="G383" s="3" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="3" t="inlineStr">
@@ -8619,8 +7829,6 @@
       </c>
       <c r="D384" s="3" t="inlineStr"/>
       <c r="E384" s="3" t="inlineStr"/>
-      <c r="F384" s="3" t="inlineStr"/>
-      <c r="G384" s="3" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="3" t="inlineStr">
@@ -8640,8 +7848,6 @@
       </c>
       <c r="D385" s="3" t="inlineStr"/>
       <c r="E385" s="3" t="inlineStr"/>
-      <c r="F385" s="3" t="inlineStr"/>
-      <c r="G385" s="3" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="3" t="inlineStr">
@@ -8661,8 +7867,6 @@
       </c>
       <c r="D386" s="3" t="inlineStr"/>
       <c r="E386" s="3" t="inlineStr"/>
-      <c r="F386" s="3" t="inlineStr"/>
-      <c r="G386" s="3" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="3" t="inlineStr">
@@ -8682,8 +7886,6 @@
       </c>
       <c r="D387" s="3" t="inlineStr"/>
       <c r="E387" s="3" t="inlineStr"/>
-      <c r="F387" s="3" t="inlineStr"/>
-      <c r="G387" s="3" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
@@ -8703,8 +7905,6 @@
       </c>
       <c r="D388" s="3" t="inlineStr"/>
       <c r="E388" s="3" t="inlineStr"/>
-      <c r="F388" s="3" t="inlineStr"/>
-      <c r="G388" s="3" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
@@ -8724,8 +7924,6 @@
       </c>
       <c r="D389" s="3" t="inlineStr"/>
       <c r="E389" s="3" t="inlineStr"/>
-      <c r="F389" s="3" t="inlineStr"/>
-      <c r="G389" s="3" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="3" t="inlineStr">
@@ -8745,8 +7943,6 @@
       </c>
       <c r="D390" s="3" t="inlineStr"/>
       <c r="E390" s="3" t="inlineStr"/>
-      <c r="F390" s="3" t="inlineStr"/>
-      <c r="G390" s="3" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="3" t="inlineStr">
@@ -8766,8 +7962,6 @@
       </c>
       <c r="D391" s="3" t="inlineStr"/>
       <c r="E391" s="3" t="inlineStr"/>
-      <c r="F391" s="3" t="inlineStr"/>
-      <c r="G391" s="3" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="3" t="inlineStr">
@@ -8787,8 +7981,6 @@
       </c>
       <c r="D392" s="3" t="inlineStr"/>
       <c r="E392" s="3" t="inlineStr"/>
-      <c r="F392" s="3" t="inlineStr"/>
-      <c r="G392" s="3" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="3" t="inlineStr">
@@ -8808,8 +8000,6 @@
       </c>
       <c r="D393" s="3" t="inlineStr"/>
       <c r="E393" s="3" t="inlineStr"/>
-      <c r="F393" s="3" t="inlineStr"/>
-      <c r="G393" s="3" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="3" t="inlineStr">
@@ -8829,8 +8019,6 @@
       </c>
       <c r="D394" s="3" t="inlineStr"/>
       <c r="E394" s="3" t="inlineStr"/>
-      <c r="F394" s="3" t="inlineStr"/>
-      <c r="G394" s="3" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="3" t="inlineStr">
@@ -8850,8 +8038,6 @@
       </c>
       <c r="D395" s="3" t="inlineStr"/>
       <c r="E395" s="3" t="inlineStr"/>
-      <c r="F395" s="3" t="inlineStr"/>
-      <c r="G395" s="3" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="3" t="inlineStr">
@@ -8871,8 +8057,6 @@
       </c>
       <c r="D396" s="3" t="inlineStr"/>
       <c r="E396" s="3" t="inlineStr"/>
-      <c r="F396" s="3" t="inlineStr"/>
-      <c r="G396" s="3" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="3" t="inlineStr">
@@ -8892,8 +8076,6 @@
       </c>
       <c r="D397" s="3" t="inlineStr"/>
       <c r="E397" s="3" t="inlineStr"/>
-      <c r="F397" s="3" t="inlineStr"/>
-      <c r="G397" s="3" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
@@ -8913,8 +8095,6 @@
       </c>
       <c r="D398" s="3" t="inlineStr"/>
       <c r="E398" s="3" t="inlineStr"/>
-      <c r="F398" s="3" t="inlineStr"/>
-      <c r="G398" s="3" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
@@ -8934,8 +8114,6 @@
       </c>
       <c r="D399" s="3" t="inlineStr"/>
       <c r="E399" s="3" t="inlineStr"/>
-      <c r="F399" s="3" t="inlineStr"/>
-      <c r="G399" s="3" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="3" t="inlineStr">
@@ -8955,8 +8133,6 @@
       </c>
       <c r="D400" s="3" t="inlineStr"/>
       <c r="E400" s="3" t="inlineStr"/>
-      <c r="F400" s="3" t="inlineStr"/>
-      <c r="G400" s="3" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="3" t="inlineStr">
@@ -8976,8 +8152,6 @@
       </c>
       <c r="D401" s="3" t="inlineStr"/>
       <c r="E401" s="3" t="inlineStr"/>
-      <c r="F401" s="3" t="inlineStr"/>
-      <c r="G401" s="3" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="3" t="inlineStr">
@@ -8997,8 +8171,6 @@
       </c>
       <c r="D402" s="3" t="inlineStr"/>
       <c r="E402" s="3" t="inlineStr"/>
-      <c r="F402" s="3" t="inlineStr"/>
-      <c r="G402" s="3" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="3" t="inlineStr">
@@ -9018,8 +8190,6 @@
       </c>
       <c r="D403" s="3" t="inlineStr"/>
       <c r="E403" s="3" t="inlineStr"/>
-      <c r="F403" s="3" t="inlineStr"/>
-      <c r="G403" s="3" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="3" t="inlineStr">
@@ -9039,8 +8209,6 @@
       </c>
       <c r="D404" s="3" t="inlineStr"/>
       <c r="E404" s="3" t="inlineStr"/>
-      <c r="F404" s="3" t="inlineStr"/>
-      <c r="G404" s="3" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="3" t="inlineStr">
@@ -9060,8 +8228,6 @@
       </c>
       <c r="D405" s="3" t="inlineStr"/>
       <c r="E405" s="3" t="inlineStr"/>
-      <c r="F405" s="3" t="inlineStr"/>
-      <c r="G405" s="3" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="3" t="inlineStr">
@@ -9081,8 +8247,6 @@
       </c>
       <c r="D406" s="3" t="inlineStr"/>
       <c r="E406" s="3" t="inlineStr"/>
-      <c r="F406" s="3" t="inlineStr"/>
-      <c r="G406" s="3" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="3" t="inlineStr">
@@ -9102,8 +8266,6 @@
       </c>
       <c r="D407" s="3" t="inlineStr"/>
       <c r="E407" s="3" t="inlineStr"/>
-      <c r="F407" s="3" t="inlineStr"/>
-      <c r="G407" s="3" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
@@ -9123,8 +8285,6 @@
       </c>
       <c r="D408" s="3" t="inlineStr"/>
       <c r="E408" s="3" t="inlineStr"/>
-      <c r="F408" s="3" t="inlineStr"/>
-      <c r="G408" s="3" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
@@ -9144,8 +8304,6 @@
       </c>
       <c r="D409" s="3" t="inlineStr"/>
       <c r="E409" s="3" t="inlineStr"/>
-      <c r="F409" s="3" t="inlineStr"/>
-      <c r="G409" s="3" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="3" t="inlineStr">
@@ -9165,8 +8323,6 @@
       </c>
       <c r="D410" s="3" t="inlineStr"/>
       <c r="E410" s="3" t="inlineStr"/>
-      <c r="F410" s="3" t="inlineStr"/>
-      <c r="G410" s="3" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="3" t="inlineStr">
@@ -9186,8 +8342,6 @@
       </c>
       <c r="D411" s="3" t="inlineStr"/>
       <c r="E411" s="3" t="inlineStr"/>
-      <c r="F411" s="3" t="inlineStr"/>
-      <c r="G411" s="3" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="3" t="inlineStr">
@@ -9207,8 +8361,6 @@
       </c>
       <c r="D412" s="3" t="inlineStr"/>
       <c r="E412" s="3" t="inlineStr"/>
-      <c r="F412" s="3" t="inlineStr"/>
-      <c r="G412" s="3" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="3" t="inlineStr">
@@ -9228,8 +8380,6 @@
       </c>
       <c r="D413" s="3" t="inlineStr"/>
       <c r="E413" s="3" t="inlineStr"/>
-      <c r="F413" s="3" t="inlineStr"/>
-      <c r="G413" s="3" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="3" t="inlineStr">
@@ -9249,8 +8399,6 @@
       </c>
       <c r="D414" s="3" t="inlineStr"/>
       <c r="E414" s="3" t="inlineStr"/>
-      <c r="F414" s="3" t="inlineStr"/>
-      <c r="G414" s="3" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
@@ -9270,8 +8418,6 @@
       </c>
       <c r="D415" s="3" t="inlineStr"/>
       <c r="E415" s="3" t="inlineStr"/>
-      <c r="F415" s="3" t="inlineStr"/>
-      <c r="G415" s="3" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="3" t="inlineStr">
@@ -9291,8 +8437,6 @@
       </c>
       <c r="D416" s="3" t="inlineStr"/>
       <c r="E416" s="3" t="inlineStr"/>
-      <c r="F416" s="3" t="inlineStr"/>
-      <c r="G416" s="3" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="3" t="inlineStr">
@@ -9312,8 +8456,6 @@
       </c>
       <c r="D417" s="3" t="inlineStr"/>
       <c r="E417" s="3" t="inlineStr"/>
-      <c r="F417" s="3" t="inlineStr"/>
-      <c r="G417" s="3" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
@@ -9333,8 +8475,6 @@
       </c>
       <c r="D418" s="3" t="inlineStr"/>
       <c r="E418" s="3" t="inlineStr"/>
-      <c r="F418" s="3" t="inlineStr"/>
-      <c r="G418" s="3" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
@@ -9354,8 +8494,6 @@
       </c>
       <c r="D419" s="3" t="inlineStr"/>
       <c r="E419" s="3" t="inlineStr"/>
-      <c r="F419" s="3" t="inlineStr"/>
-      <c r="G419" s="3" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="3" t="inlineStr">
@@ -9375,8 +8513,6 @@
       </c>
       <c r="D420" s="3" t="inlineStr"/>
       <c r="E420" s="3" t="inlineStr"/>
-      <c r="F420" s="3" t="inlineStr"/>
-      <c r="G420" s="3" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="3" t="inlineStr">
@@ -9396,8 +8532,6 @@
       </c>
       <c r="D421" s="3" t="inlineStr"/>
       <c r="E421" s="3" t="inlineStr"/>
-      <c r="F421" s="3" t="inlineStr"/>
-      <c r="G421" s="3" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="3" t="inlineStr">
@@ -9417,8 +8551,6 @@
       </c>
       <c r="D422" s="3" t="inlineStr"/>
       <c r="E422" s="3" t="inlineStr"/>
-      <c r="F422" s="3" t="inlineStr"/>
-      <c r="G422" s="3" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="3" t="inlineStr">
@@ -9438,8 +8570,6 @@
       </c>
       <c r="D423" s="3" t="inlineStr"/>
       <c r="E423" s="3" t="inlineStr"/>
-      <c r="F423" s="3" t="inlineStr"/>
-      <c r="G423" s="3" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="3" t="inlineStr">
@@ -9459,8 +8589,6 @@
       </c>
       <c r="D424" s="3" t="inlineStr"/>
       <c r="E424" s="3" t="inlineStr"/>
-      <c r="F424" s="3" t="inlineStr"/>
-      <c r="G424" s="3" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="3" t="inlineStr">
@@ -9480,8 +8608,6 @@
       </c>
       <c r="D425" s="3" t="inlineStr"/>
       <c r="E425" s="3" t="inlineStr"/>
-      <c r="F425" s="3" t="inlineStr"/>
-      <c r="G425" s="3" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="3" t="inlineStr">
@@ -9501,8 +8627,6 @@
       </c>
       <c r="D426" s="3" t="inlineStr"/>
       <c r="E426" s="3" t="inlineStr"/>
-      <c r="F426" s="3" t="inlineStr"/>
-      <c r="G426" s="3" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="3" t="inlineStr">
@@ -9522,8 +8646,6 @@
       </c>
       <c r="D427" s="3" t="inlineStr"/>
       <c r="E427" s="3" t="inlineStr"/>
-      <c r="F427" s="3" t="inlineStr"/>
-      <c r="G427" s="3" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="3" t="inlineStr">
@@ -9543,8 +8665,6 @@
       </c>
       <c r="D428" s="3" t="inlineStr"/>
       <c r="E428" s="3" t="inlineStr"/>
-      <c r="F428" s="3" t="inlineStr"/>
-      <c r="G428" s="3" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="3" t="inlineStr">
@@ -9564,8 +8684,6 @@
       </c>
       <c r="D429" s="3" t="inlineStr"/>
       <c r="E429" s="3" t="inlineStr"/>
-      <c r="F429" s="3" t="inlineStr"/>
-      <c r="G429" s="3" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="3" t="inlineStr">
@@ -9585,8 +8703,6 @@
       </c>
       <c r="D430" s="3" t="inlineStr"/>
       <c r="E430" s="3" t="inlineStr"/>
-      <c r="F430" s="3" t="inlineStr"/>
-      <c r="G430" s="3" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="3" t="inlineStr">
@@ -9606,8 +8722,6 @@
       </c>
       <c r="D431" s="3" t="inlineStr"/>
       <c r="E431" s="3" t="inlineStr"/>
-      <c r="F431" s="3" t="inlineStr"/>
-      <c r="G431" s="3" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="3" t="inlineStr">
@@ -9627,8 +8741,6 @@
       </c>
       <c r="D432" s="3" t="inlineStr"/>
       <c r="E432" s="3" t="inlineStr"/>
-      <c r="F432" s="3" t="inlineStr"/>
-      <c r="G432" s="3" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
@@ -9648,8 +8760,6 @@
       </c>
       <c r="D433" s="3" t="inlineStr"/>
       <c r="E433" s="3" t="inlineStr"/>
-      <c r="F433" s="3" t="inlineStr"/>
-      <c r="G433" s="3" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
@@ -9669,8 +8779,6 @@
       </c>
       <c r="D434" s="3" t="inlineStr"/>
       <c r="E434" s="3" t="inlineStr"/>
-      <c r="F434" s="3" t="inlineStr"/>
-      <c r="G434" s="3" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
@@ -9690,8 +8798,6 @@
       </c>
       <c r="D435" s="3" t="inlineStr"/>
       <c r="E435" s="3" t="inlineStr"/>
-      <c r="F435" s="3" t="inlineStr"/>
-      <c r="G435" s="3" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
@@ -9711,8 +8817,6 @@
       </c>
       <c r="D436" s="3" t="inlineStr"/>
       <c r="E436" s="3" t="inlineStr"/>
-      <c r="F436" s="3" t="inlineStr"/>
-      <c r="G436" s="3" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="3" t="inlineStr">
@@ -9732,8 +8836,6 @@
       </c>
       <c r="D437" s="3" t="inlineStr"/>
       <c r="E437" s="3" t="inlineStr"/>
-      <c r="F437" s="3" t="inlineStr"/>
-      <c r="G437" s="3" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="3" t="inlineStr">
@@ -9753,8 +8855,6 @@
       </c>
       <c r="D438" s="3" t="inlineStr"/>
       <c r="E438" s="3" t="inlineStr"/>
-      <c r="F438" s="3" t="inlineStr"/>
-      <c r="G438" s="3" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="3" t="inlineStr">
@@ -9774,8 +8874,6 @@
       </c>
       <c r="D439" s="3" t="inlineStr"/>
       <c r="E439" s="3" t="inlineStr"/>
-      <c r="F439" s="3" t="inlineStr"/>
-      <c r="G439" s="3" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
@@ -9795,8 +8893,6 @@
       </c>
       <c r="D440" s="3" t="inlineStr"/>
       <c r="E440" s="3" t="inlineStr"/>
-      <c r="F440" s="3" t="inlineStr"/>
-      <c r="G440" s="3" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="3" t="inlineStr">
@@ -9816,8 +8912,6 @@
       </c>
       <c r="D441" s="3" t="inlineStr"/>
       <c r="E441" s="3" t="inlineStr"/>
-      <c r="F441" s="3" t="inlineStr"/>
-      <c r="G441" s="3" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="3" t="inlineStr">
@@ -9837,8 +8931,6 @@
       </c>
       <c r="D442" s="3" t="inlineStr"/>
       <c r="E442" s="3" t="inlineStr"/>
-      <c r="F442" s="3" t="inlineStr"/>
-      <c r="G442" s="3" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="3" t="inlineStr">
@@ -9858,8 +8950,6 @@
       </c>
       <c r="D443" s="3" t="inlineStr"/>
       <c r="E443" s="3" t="inlineStr"/>
-      <c r="F443" s="3" t="inlineStr"/>
-      <c r="G443" s="3" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="3" t="inlineStr">
@@ -9879,8 +8969,6 @@
       </c>
       <c r="D444" s="3" t="inlineStr"/>
       <c r="E444" s="3" t="inlineStr"/>
-      <c r="F444" s="3" t="inlineStr"/>
-      <c r="G444" s="3" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="3" t="inlineStr">
@@ -9900,8 +8988,6 @@
       </c>
       <c r="D445" s="3" t="inlineStr"/>
       <c r="E445" s="3" t="inlineStr"/>
-      <c r="F445" s="3" t="inlineStr"/>
-      <c r="G445" s="3" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="3" t="inlineStr">
@@ -9921,8 +9007,6 @@
       </c>
       <c r="D446" s="3" t="inlineStr"/>
       <c r="E446" s="3" t="inlineStr"/>
-      <c r="F446" s="3" t="inlineStr"/>
-      <c r="G446" s="3" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="3" t="inlineStr">
@@ -9942,8 +9026,6 @@
       </c>
       <c r="D447" s="3" t="inlineStr"/>
       <c r="E447" s="3" t="inlineStr"/>
-      <c r="F447" s="3" t="inlineStr"/>
-      <c r="G447" s="3" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
@@ -9963,8 +9045,6 @@
       </c>
       <c r="D448" s="3" t="inlineStr"/>
       <c r="E448" s="3" t="inlineStr"/>
-      <c r="F448" s="3" t="inlineStr"/>
-      <c r="G448" s="3" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="3" t="inlineStr">
@@ -9984,8 +9064,6 @@
       </c>
       <c r="D449" s="3" t="inlineStr"/>
       <c r="E449" s="3" t="inlineStr"/>
-      <c r="F449" s="3" t="inlineStr"/>
-      <c r="G449" s="3" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
@@ -10005,8 +9083,6 @@
       </c>
       <c r="D450" s="3" t="inlineStr"/>
       <c r="E450" s="3" t="inlineStr"/>
-      <c r="F450" s="3" t="inlineStr"/>
-      <c r="G450" s="3" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="3" t="inlineStr">
@@ -10026,8 +9102,6 @@
       </c>
       <c r="D451" s="3" t="inlineStr"/>
       <c r="E451" s="3" t="inlineStr"/>
-      <c r="F451" s="3" t="inlineStr"/>
-      <c r="G451" s="3" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="3" t="inlineStr">
@@ -10047,8 +9121,6 @@
       </c>
       <c r="D452" s="3" t="inlineStr"/>
       <c r="E452" s="3" t="inlineStr"/>
-      <c r="F452" s="3" t="inlineStr"/>
-      <c r="G452" s="3" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
@@ -10068,8 +9140,6 @@
       </c>
       <c r="D453" s="3" t="inlineStr"/>
       <c r="E453" s="3" t="inlineStr"/>
-      <c r="F453" s="3" t="inlineStr"/>
-      <c r="G453" s="3" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
@@ -10089,8 +9159,6 @@
       </c>
       <c r="D454" s="3" t="inlineStr"/>
       <c r="E454" s="3" t="inlineStr"/>
-      <c r="F454" s="3" t="inlineStr"/>
-      <c r="G454" s="3" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="3" t="inlineStr">
@@ -10110,8 +9178,6 @@
       </c>
       <c r="D455" s="3" t="inlineStr"/>
       <c r="E455" s="3" t="inlineStr"/>
-      <c r="F455" s="3" t="inlineStr"/>
-      <c r="G455" s="3" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="3" t="inlineStr">
@@ -10131,8 +9197,6 @@
       </c>
       <c r="D456" s="3" t="inlineStr"/>
       <c r="E456" s="3" t="inlineStr"/>
-      <c r="F456" s="3" t="inlineStr"/>
-      <c r="G456" s="3" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="3" t="inlineStr">
@@ -10152,8 +9216,6 @@
       </c>
       <c r="D457" s="3" t="inlineStr"/>
       <c r="E457" s="3" t="inlineStr"/>
-      <c r="F457" s="3" t="inlineStr"/>
-      <c r="G457" s="3" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
@@ -10173,8 +9235,6 @@
       </c>
       <c r="D458" s="3" t="inlineStr"/>
       <c r="E458" s="3" t="inlineStr"/>
-      <c r="F458" s="3" t="inlineStr"/>
-      <c r="G458" s="3" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="inlineStr">
@@ -10194,8 +9254,6 @@
       </c>
       <c r="D459" s="3" t="inlineStr"/>
       <c r="E459" s="3" t="inlineStr"/>
-      <c r="F459" s="3" t="inlineStr"/>
-      <c r="G459" s="3" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="3" t="inlineStr">
@@ -10215,8 +9273,6 @@
       </c>
       <c r="D460" s="3" t="inlineStr"/>
       <c r="E460" s="3" t="inlineStr"/>
-      <c r="F460" s="3" t="inlineStr"/>
-      <c r="G460" s="3" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="3" t="inlineStr">
@@ -10236,8 +9292,6 @@
       </c>
       <c r="D461" s="3" t="inlineStr"/>
       <c r="E461" s="3" t="inlineStr"/>
-      <c r="F461" s="3" t="inlineStr"/>
-      <c r="G461" s="3" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="3" t="inlineStr">
@@ -10257,8 +9311,6 @@
       </c>
       <c r="D462" s="3" t="inlineStr"/>
       <c r="E462" s="3" t="inlineStr"/>
-      <c r="F462" s="3" t="inlineStr"/>
-      <c r="G462" s="3" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="3" t="inlineStr">
@@ -10278,8 +9330,6 @@
       </c>
       <c r="D463" s="3" t="inlineStr"/>
       <c r="E463" s="3" t="inlineStr"/>
-      <c r="F463" s="3" t="inlineStr"/>
-      <c r="G463" s="3" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="3" t="inlineStr">
@@ -10299,8 +9349,6 @@
       </c>
       <c r="D464" s="3" t="inlineStr"/>
       <c r="E464" s="3" t="inlineStr"/>
-      <c r="F464" s="3" t="inlineStr"/>
-      <c r="G464" s="3" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="3" t="inlineStr">
@@ -10320,8 +9368,6 @@
       </c>
       <c r="D465" s="3" t="inlineStr"/>
       <c r="E465" s="3" t="inlineStr"/>
-      <c r="F465" s="3" t="inlineStr"/>
-      <c r="G465" s="3" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="3" t="inlineStr">
@@ -10341,8 +9387,6 @@
       </c>
       <c r="D466" s="3" t="inlineStr"/>
       <c r="E466" s="3" t="inlineStr"/>
-      <c r="F466" s="3" t="inlineStr"/>
-      <c r="G466" s="3" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="3" t="inlineStr">
@@ -10362,8 +9406,6 @@
       </c>
       <c r="D467" s="3" t="inlineStr"/>
       <c r="E467" s="3" t="inlineStr"/>
-      <c r="F467" s="3" t="inlineStr"/>
-      <c r="G467" s="3" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="3" t="inlineStr">
@@ -10383,8 +9425,6 @@
       </c>
       <c r="D468" s="3" t="inlineStr"/>
       <c r="E468" s="3" t="inlineStr"/>
-      <c r="F468" s="3" t="inlineStr"/>
-      <c r="G468" s="3" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="3" t="inlineStr">
@@ -10404,8 +9444,6 @@
       </c>
       <c r="D469" s="3" t="inlineStr"/>
       <c r="E469" s="3" t="inlineStr"/>
-      <c r="F469" s="3" t="inlineStr"/>
-      <c r="G469" s="3" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="3" t="inlineStr">
@@ -10425,8 +9463,6 @@
       </c>
       <c r="D470" s="3" t="inlineStr"/>
       <c r="E470" s="3" t="inlineStr"/>
-      <c r="F470" s="3" t="inlineStr"/>
-      <c r="G470" s="3" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="3" t="inlineStr">
@@ -10446,8 +9482,6 @@
       </c>
       <c r="D471" s="3" t="inlineStr"/>
       <c r="E471" s="3" t="inlineStr"/>
-      <c r="F471" s="3" t="inlineStr"/>
-      <c r="G471" s="3" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="3" t="inlineStr">
@@ -10467,8 +9501,6 @@
       </c>
       <c r="D472" s="3" t="inlineStr"/>
       <c r="E472" s="3" t="inlineStr"/>
-      <c r="F472" s="3" t="inlineStr"/>
-      <c r="G472" s="3" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="3" t="inlineStr">
@@ -10488,8 +9520,6 @@
       </c>
       <c r="D473" s="3" t="inlineStr"/>
       <c r="E473" s="3" t="inlineStr"/>
-      <c r="F473" s="3" t="inlineStr"/>
-      <c r="G473" s="3" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="3" t="inlineStr">
@@ -10509,8 +9539,6 @@
       </c>
       <c r="D474" s="3" t="inlineStr"/>
       <c r="E474" s="3" t="inlineStr"/>
-      <c r="F474" s="3" t="inlineStr"/>
-      <c r="G474" s="3" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="3" t="inlineStr">
@@ -10530,8 +9558,6 @@
       </c>
       <c r="D475" s="3" t="inlineStr"/>
       <c r="E475" s="3" t="inlineStr"/>
-      <c r="F475" s="3" t="inlineStr"/>
-      <c r="G475" s="3" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
@@ -10551,8 +9577,6 @@
       </c>
       <c r="D476" s="3" t="inlineStr"/>
       <c r="E476" s="3" t="inlineStr"/>
-      <c r="F476" s="3" t="inlineStr"/>
-      <c r="G476" s="3" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="3" t="inlineStr">
@@ -10572,8 +9596,6 @@
       </c>
       <c r="D477" s="3" t="inlineStr"/>
       <c r="E477" s="3" t="inlineStr"/>
-      <c r="F477" s="3" t="inlineStr"/>
-      <c r="G477" s="3" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="3" t="inlineStr">
@@ -10593,8 +9615,6 @@
       </c>
       <c r="D478" s="3" t="inlineStr"/>
       <c r="E478" s="3" t="inlineStr"/>
-      <c r="F478" s="3" t="inlineStr"/>
-      <c r="G478" s="3" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="3" t="inlineStr">
@@ -10614,8 +9634,6 @@
       </c>
       <c r="D479" s="3" t="inlineStr"/>
       <c r="E479" s="3" t="inlineStr"/>
-      <c r="F479" s="3" t="inlineStr"/>
-      <c r="G479" s="3" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
@@ -10635,8 +9653,6 @@
       </c>
       <c r="D480" s="3" t="inlineStr"/>
       <c r="E480" s="3" t="inlineStr"/>
-      <c r="F480" s="3" t="inlineStr"/>
-      <c r="G480" s="3" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="3" t="inlineStr">
@@ -10656,8 +9672,6 @@
       </c>
       <c r="D481" s="3" t="inlineStr"/>
       <c r="E481" s="3" t="inlineStr"/>
-      <c r="F481" s="3" t="inlineStr"/>
-      <c r="G481" s="3" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="3" t="inlineStr">
@@ -10677,8 +9691,6 @@
       </c>
       <c r="D482" s="3" t="inlineStr"/>
       <c r="E482" s="3" t="inlineStr"/>
-      <c r="F482" s="3" t="inlineStr"/>
-      <c r="G482" s="3" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="3" t="inlineStr">
@@ -10698,8 +9710,6 @@
       </c>
       <c r="D483" s="3" t="inlineStr"/>
       <c r="E483" s="3" t="inlineStr"/>
-      <c r="F483" s="3" t="inlineStr"/>
-      <c r="G483" s="3" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="3" t="inlineStr">
@@ -10719,8 +9729,6 @@
       </c>
       <c r="D484" s="3" t="inlineStr"/>
       <c r="E484" s="3" t="inlineStr"/>
-      <c r="F484" s="3" t="inlineStr"/>
-      <c r="G484" s="3" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
@@ -10740,8 +9748,6 @@
       </c>
       <c r="D485" s="3" t="inlineStr"/>
       <c r="E485" s="3" t="inlineStr"/>
-      <c r="F485" s="3" t="inlineStr"/>
-      <c r="G485" s="3" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
@@ -10761,8 +9767,6 @@
       </c>
       <c r="D486" s="3" t="inlineStr"/>
       <c r="E486" s="3" t="inlineStr"/>
-      <c r="F486" s="3" t="inlineStr"/>
-      <c r="G486" s="3" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="3" t="inlineStr">
@@ -10782,8 +9786,6 @@
       </c>
       <c r="D487" s="3" t="inlineStr"/>
       <c r="E487" s="3" t="inlineStr"/>
-      <c r="F487" s="3" t="inlineStr"/>
-      <c r="G487" s="3" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="3" t="inlineStr">
@@ -10803,8 +9805,6 @@
       </c>
       <c r="D488" s="3" t="inlineStr"/>
       <c r="E488" s="3" t="inlineStr"/>
-      <c r="F488" s="3" t="inlineStr"/>
-      <c r="G488" s="3" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="3" t="inlineStr">
@@ -10824,8 +9824,6 @@
       </c>
       <c r="D489" s="3" t="inlineStr"/>
       <c r="E489" s="3" t="inlineStr"/>
-      <c r="F489" s="3" t="inlineStr"/>
-      <c r="G489" s="3" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="3" t="inlineStr">
@@ -10845,8 +9843,6 @@
       </c>
       <c r="D490" s="3" t="inlineStr"/>
       <c r="E490" s="3" t="inlineStr"/>
-      <c r="F490" s="3" t="inlineStr"/>
-      <c r="G490" s="3" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="3" t="inlineStr">
@@ -10866,8 +9862,6 @@
       </c>
       <c r="D491" s="3" t="inlineStr"/>
       <c r="E491" s="3" t="inlineStr"/>
-      <c r="F491" s="3" t="inlineStr"/>
-      <c r="G491" s="3" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="3" t="inlineStr">
@@ -10887,8 +9881,6 @@
       </c>
       <c r="D492" s="3" t="inlineStr"/>
       <c r="E492" s="3" t="inlineStr"/>
-      <c r="F492" s="3" t="inlineStr"/>
-      <c r="G492" s="3" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="3" t="inlineStr">
@@ -10908,8 +9900,6 @@
       </c>
       <c r="D493" s="3" t="inlineStr"/>
       <c r="E493" s="3" t="inlineStr"/>
-      <c r="F493" s="3" t="inlineStr"/>
-      <c r="G493" s="3" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="3" t="inlineStr">
@@ -10929,8 +9919,6 @@
       </c>
       <c r="D494" s="3" t="inlineStr"/>
       <c r="E494" s="3" t="inlineStr"/>
-      <c r="F494" s="3" t="inlineStr"/>
-      <c r="G494" s="3" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="3" t="inlineStr">
@@ -10950,8 +9938,6 @@
       </c>
       <c r="D495" s="3" t="inlineStr"/>
       <c r="E495" s="3" t="inlineStr"/>
-      <c r="F495" s="3" t="inlineStr"/>
-      <c r="G495" s="3" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="3" t="inlineStr">
@@ -10971,8 +9957,6 @@
       </c>
       <c r="D496" s="3" t="inlineStr"/>
       <c r="E496" s="3" t="inlineStr"/>
-      <c r="F496" s="3" t="inlineStr"/>
-      <c r="G496" s="3" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="3" t="inlineStr">
@@ -10992,8 +9976,6 @@
       </c>
       <c r="D497" s="3" t="inlineStr"/>
       <c r="E497" s="3" t="inlineStr"/>
-      <c r="F497" s="3" t="inlineStr"/>
-      <c r="G497" s="3" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="3" t="inlineStr">
@@ -11013,8 +9995,6 @@
       </c>
       <c r="D498" s="3" t="inlineStr"/>
       <c r="E498" s="3" t="inlineStr"/>
-      <c r="F498" s="3" t="inlineStr"/>
-      <c r="G498" s="3" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" s="3" t="inlineStr">
@@ -11034,8 +10014,6 @@
       </c>
       <c r="D499" s="3" t="inlineStr"/>
       <c r="E499" s="3" t="inlineStr"/>
-      <c r="F499" s="3" t="inlineStr"/>
-      <c r="G499" s="3" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
@@ -11055,8 +10033,6 @@
       </c>
       <c r="D500" s="3" t="inlineStr"/>
       <c r="E500" s="3" t="inlineStr"/>
-      <c r="F500" s="3" t="inlineStr"/>
-      <c r="G500" s="3" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" s="3" t="inlineStr">
@@ -11076,8 +10052,6 @@
       </c>
       <c r="D501" s="3" t="inlineStr"/>
       <c r="E501" s="3" t="inlineStr"/>
-      <c r="F501" s="3" t="inlineStr"/>
-      <c r="G501" s="3" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" s="3" t="inlineStr">
@@ -11097,8 +10071,6 @@
       </c>
       <c r="D502" s="3" t="inlineStr"/>
       <c r="E502" s="3" t="inlineStr"/>
-      <c r="F502" s="3" t="inlineStr"/>
-      <c r="G502" s="3" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" s="3" t="inlineStr">
@@ -11118,8 +10090,6 @@
       </c>
       <c r="D503" s="3" t="inlineStr"/>
       <c r="E503" s="3" t="inlineStr"/>
-      <c r="F503" s="3" t="inlineStr"/>
-      <c r="G503" s="3" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
@@ -11139,8 +10109,6 @@
       </c>
       <c r="D504" s="3" t="inlineStr"/>
       <c r="E504" s="3" t="inlineStr"/>
-      <c r="F504" s="3" t="inlineStr"/>
-      <c r="G504" s="3" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" s="3" t="inlineStr">
@@ -11160,8 +10128,6 @@
       </c>
       <c r="D505" s="3" t="inlineStr"/>
       <c r="E505" s="3" t="inlineStr"/>
-      <c r="F505" s="3" t="inlineStr"/>
-      <c r="G505" s="3" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" s="3" t="inlineStr">
@@ -11181,8 +10147,6 @@
       </c>
       <c r="D506" s="3" t="inlineStr"/>
       <c r="E506" s="3" t="inlineStr"/>
-      <c r="F506" s="3" t="inlineStr"/>
-      <c r="G506" s="3" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
@@ -11202,8 +10166,6 @@
       </c>
       <c r="D507" s="3" t="inlineStr"/>
       <c r="E507" s="3" t="inlineStr"/>
-      <c r="F507" s="3" t="inlineStr"/>
-      <c r="G507" s="3" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" s="3" t="inlineStr">
@@ -11223,8 +10185,6 @@
       </c>
       <c r="D508" s="3" t="inlineStr"/>
       <c r="E508" s="3" t="inlineStr"/>
-      <c r="F508" s="3" t="inlineStr"/>
-      <c r="G508" s="3" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="3" t="inlineStr">
@@ -11244,8 +10204,6 @@
       </c>
       <c r="D509" s="3" t="inlineStr"/>
       <c r="E509" s="3" t="inlineStr"/>
-      <c r="F509" s="3" t="inlineStr"/>
-      <c r="G509" s="3" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" s="3" t="inlineStr">
@@ -11265,8 +10223,6 @@
       </c>
       <c r="D510" s="3" t="inlineStr"/>
       <c r="E510" s="3" t="inlineStr"/>
-      <c r="F510" s="3" t="inlineStr"/>
-      <c r="G510" s="3" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" s="3" t="inlineStr">
@@ -11286,8 +10242,6 @@
       </c>
       <c r="D511" s="3" t="inlineStr"/>
       <c r="E511" s="3" t="inlineStr"/>
-      <c r="F511" s="3" t="inlineStr"/>
-      <c r="G511" s="3" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" s="3" t="inlineStr">
@@ -11307,8 +10261,6 @@
       </c>
       <c r="D512" s="3" t="inlineStr"/>
       <c r="E512" s="3" t="inlineStr"/>
-      <c r="F512" s="3" t="inlineStr"/>
-      <c r="G512" s="3" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" s="3" t="inlineStr">
@@ -11328,8 +10280,6 @@
       </c>
       <c r="D513" s="3" t="inlineStr"/>
       <c r="E513" s="3" t="inlineStr"/>
-      <c r="F513" s="3" t="inlineStr"/>
-      <c r="G513" s="3" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" s="3" t="inlineStr">
@@ -11349,8 +10299,6 @@
       </c>
       <c r="D514" s="3" t="inlineStr"/>
       <c r="E514" s="3" t="inlineStr"/>
-      <c r="F514" s="3" t="inlineStr"/>
-      <c r="G514" s="3" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" s="3" t="inlineStr">
@@ -11370,8 +10318,6 @@
       </c>
       <c r="D515" s="3" t="inlineStr"/>
       <c r="E515" s="3" t="inlineStr"/>
-      <c r="F515" s="3" t="inlineStr"/>
-      <c r="G515" s="3" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" s="3" t="inlineStr">
@@ -11391,8 +10337,6 @@
       </c>
       <c r="D516" s="3" t="inlineStr"/>
       <c r="E516" s="3" t="inlineStr"/>
-      <c r="F516" s="3" t="inlineStr"/>
-      <c r="G516" s="3" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" s="3" t="inlineStr">
@@ -11412,8 +10356,6 @@
       </c>
       <c r="D517" s="3" t="inlineStr"/>
       <c r="E517" s="3" t="inlineStr"/>
-      <c r="F517" s="3" t="inlineStr"/>
-      <c r="G517" s="3" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" s="3" t="inlineStr">
@@ -11433,8 +10375,6 @@
       </c>
       <c r="D518" s="3" t="inlineStr"/>
       <c r="E518" s="3" t="inlineStr"/>
-      <c r="F518" s="3" t="inlineStr"/>
-      <c r="G518" s="3" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" s="3" t="inlineStr">
@@ -11454,8 +10394,6 @@
       </c>
       <c r="D519" s="3" t="inlineStr"/>
       <c r="E519" s="3" t="inlineStr"/>
-      <c r="F519" s="3" t="inlineStr"/>
-      <c r="G519" s="3" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="3" t="inlineStr">
@@ -11475,8 +10413,6 @@
       </c>
       <c r="D520" s="3" t="inlineStr"/>
       <c r="E520" s="3" t="inlineStr"/>
-      <c r="F520" s="3" t="inlineStr"/>
-      <c r="G520" s="3" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="3" t="inlineStr">
@@ -11496,8 +10432,6 @@
       </c>
       <c r="D521" s="3" t="inlineStr"/>
       <c r="E521" s="3" t="inlineStr"/>
-      <c r="F521" s="3" t="inlineStr"/>
-      <c r="G521" s="3" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="3" t="inlineStr">
@@ -11517,8 +10451,6 @@
       </c>
       <c r="D522" s="3" t="inlineStr"/>
       <c r="E522" s="3" t="inlineStr"/>
-      <c r="F522" s="3" t="inlineStr"/>
-      <c r="G522" s="3" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" s="3" t="inlineStr">
@@ -11538,8 +10470,6 @@
       </c>
       <c r="D523" s="3" t="inlineStr"/>
       <c r="E523" s="3" t="inlineStr"/>
-      <c r="F523" s="3" t="inlineStr"/>
-      <c r="G523" s="3" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="3" t="inlineStr">
@@ -11559,8 +10489,6 @@
       </c>
       <c r="D524" s="3" t="inlineStr"/>
       <c r="E524" s="3" t="inlineStr"/>
-      <c r="F524" s="3" t="inlineStr"/>
-      <c r="G524" s="3" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="3" t="inlineStr">
@@ -11580,8 +10508,6 @@
       </c>
       <c r="D525" s="3" t="inlineStr"/>
       <c r="E525" s="3" t="inlineStr"/>
-      <c r="F525" s="3" t="inlineStr"/>
-      <c r="G525" s="3" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" s="3" t="inlineStr">
@@ -11601,8 +10527,6 @@
       </c>
       <c r="D526" s="3" t="inlineStr"/>
       <c r="E526" s="3" t="inlineStr"/>
-      <c r="F526" s="3" t="inlineStr"/>
-      <c r="G526" s="3" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" s="3" t="inlineStr">
@@ -11622,8 +10546,6 @@
       </c>
       <c r="D527" s="3" t="inlineStr"/>
       <c r="E527" s="3" t="inlineStr"/>
-      <c r="F527" s="3" t="inlineStr"/>
-      <c r="G527" s="3" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="3" t="inlineStr">
@@ -11643,8 +10565,6 @@
       </c>
       <c r="D528" s="3" t="inlineStr"/>
       <c r="E528" s="3" t="inlineStr"/>
-      <c r="F528" s="3" t="inlineStr"/>
-      <c r="G528" s="3" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" s="3" t="inlineStr">
@@ -11664,8 +10584,6 @@
       </c>
       <c r="D529" s="3" t="inlineStr"/>
       <c r="E529" s="3" t="inlineStr"/>
-      <c r="F529" s="3" t="inlineStr"/>
-      <c r="G529" s="3" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="3" t="inlineStr">
@@ -11685,8 +10603,6 @@
       </c>
       <c r="D530" s="3" t="inlineStr"/>
       <c r="E530" s="3" t="inlineStr"/>
-      <c r="F530" s="3" t="inlineStr"/>
-      <c r="G530" s="3" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" s="3" t="inlineStr">
@@ -11706,8 +10622,6 @@
       </c>
       <c r="D531" s="3" t="inlineStr"/>
       <c r="E531" s="3" t="inlineStr"/>
-      <c r="F531" s="3" t="inlineStr"/>
-      <c r="G531" s="3" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" s="3" t="inlineStr">
@@ -11727,8 +10641,6 @@
       </c>
       <c r="D532" s="3" t="inlineStr"/>
       <c r="E532" s="3" t="inlineStr"/>
-      <c r="F532" s="3" t="inlineStr"/>
-      <c r="G532" s="3" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="3" t="inlineStr">
@@ -11748,8 +10660,6 @@
       </c>
       <c r="D533" s="3" t="inlineStr"/>
       <c r="E533" s="3" t="inlineStr"/>
-      <c r="F533" s="3" t="inlineStr"/>
-      <c r="G533" s="3" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="3" t="inlineStr">
@@ -11769,8 +10679,6 @@
       </c>
       <c r="D534" s="3" t="inlineStr"/>
       <c r="E534" s="3" t="inlineStr"/>
-      <c r="F534" s="3" t="inlineStr"/>
-      <c r="G534" s="3" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="3" t="inlineStr">
@@ -11790,8 +10698,6 @@
       </c>
       <c r="D535" s="3" t="inlineStr"/>
       <c r="E535" s="3" t="inlineStr"/>
-      <c r="F535" s="3" t="inlineStr"/>
-      <c r="G535" s="3" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="3" t="inlineStr">
@@ -11811,8 +10717,6 @@
       </c>
       <c r="D536" s="3" t="inlineStr"/>
       <c r="E536" s="3" t="inlineStr"/>
-      <c r="F536" s="3" t="inlineStr"/>
-      <c r="G536" s="3" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="3" t="inlineStr">
@@ -11832,8 +10736,6 @@
       </c>
       <c r="D537" s="3" t="inlineStr"/>
       <c r="E537" s="3" t="inlineStr"/>
-      <c r="F537" s="3" t="inlineStr"/>
-      <c r="G537" s="3" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="3" t="inlineStr">
@@ -11853,8 +10755,6 @@
       </c>
       <c r="D538" s="3" t="inlineStr"/>
       <c r="E538" s="3" t="inlineStr"/>
-      <c r="F538" s="3" t="inlineStr"/>
-      <c r="G538" s="3" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="3" t="inlineStr">
@@ -11874,8 +10774,6 @@
       </c>
       <c r="D539" s="3" t="inlineStr"/>
       <c r="E539" s="3" t="inlineStr"/>
-      <c r="F539" s="3" t="inlineStr"/>
-      <c r="G539" s="3" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="3" t="inlineStr">
@@ -11895,8 +10793,6 @@
       </c>
       <c r="D540" s="3" t="inlineStr"/>
       <c r="E540" s="3" t="inlineStr"/>
-      <c r="F540" s="3" t="inlineStr"/>
-      <c r="G540" s="3" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="3" t="inlineStr">
@@ -11916,8 +10812,6 @@
       </c>
       <c r="D541" s="3" t="inlineStr"/>
       <c r="E541" s="3" t="inlineStr"/>
-      <c r="F541" s="3" t="inlineStr"/>
-      <c r="G541" s="3" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="3" t="inlineStr">
@@ -11937,8 +10831,6 @@
       </c>
       <c r="D542" s="3" t="inlineStr"/>
       <c r="E542" s="3" t="inlineStr"/>
-      <c r="F542" s="3" t="inlineStr"/>
-      <c r="G542" s="3" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" s="3" t="inlineStr">
@@ -11958,8 +10850,6 @@
       </c>
       <c r="D543" s="3" t="inlineStr"/>
       <c r="E543" s="3" t="inlineStr"/>
-      <c r="F543" s="3" t="inlineStr"/>
-      <c r="G543" s="3" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="3" t="inlineStr">
@@ -11979,8 +10869,6 @@
       </c>
       <c r="D544" s="3" t="inlineStr"/>
       <c r="E544" s="3" t="inlineStr"/>
-      <c r="F544" s="3" t="inlineStr"/>
-      <c r="G544" s="3" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="3" t="inlineStr">
@@ -12000,8 +10888,6 @@
       </c>
       <c r="D545" s="3" t="inlineStr"/>
       <c r="E545" s="3" t="inlineStr"/>
-      <c r="F545" s="3" t="inlineStr"/>
-      <c r="G545" s="3" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="3" t="inlineStr">
@@ -12021,8 +10907,6 @@
       </c>
       <c r="D546" s="3" t="inlineStr"/>
       <c r="E546" s="3" t="inlineStr"/>
-      <c r="F546" s="3" t="inlineStr"/>
-      <c r="G546" s="3" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="3" t="inlineStr">
@@ -12042,8 +10926,6 @@
       </c>
       <c r="D547" s="3" t="inlineStr"/>
       <c r="E547" s="3" t="inlineStr"/>
-      <c r="F547" s="3" t="inlineStr"/>
-      <c r="G547" s="3" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" s="3" t="inlineStr">
@@ -12063,8 +10945,6 @@
       </c>
       <c r="D548" s="3" t="inlineStr"/>
       <c r="E548" s="3" t="inlineStr"/>
-      <c r="F548" s="3" t="inlineStr"/>
-      <c r="G548" s="3" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="3" t="inlineStr">
@@ -12084,8 +10964,6 @@
       </c>
       <c r="D549" s="3" t="inlineStr"/>
       <c r="E549" s="3" t="inlineStr"/>
-      <c r="F549" s="3" t="inlineStr"/>
-      <c r="G549" s="3" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="3" t="inlineStr">
@@ -12105,8 +10983,6 @@
       </c>
       <c r="D550" s="3" t="inlineStr"/>
       <c r="E550" s="3" t="inlineStr"/>
-      <c r="F550" s="3" t="inlineStr"/>
-      <c r="G550" s="3" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="3" t="inlineStr">
@@ -12126,8 +11002,6 @@
       </c>
       <c r="D551" s="3" t="inlineStr"/>
       <c r="E551" s="3" t="inlineStr"/>
-      <c r="F551" s="3" t="inlineStr"/>
-      <c r="G551" s="3" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="3" t="inlineStr">
@@ -12147,8 +11021,6 @@
       </c>
       <c r="D552" s="3" t="inlineStr"/>
       <c r="E552" s="3" t="inlineStr"/>
-      <c r="F552" s="3" t="inlineStr"/>
-      <c r="G552" s="3" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" s="3" t="inlineStr">
@@ -12168,8 +11040,6 @@
       </c>
       <c r="D553" s="3" t="inlineStr"/>
       <c r="E553" s="3" t="inlineStr"/>
-      <c r="F553" s="3" t="inlineStr"/>
-      <c r="G553" s="3" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="3" t="inlineStr">
@@ -12189,8 +11059,6 @@
       </c>
       <c r="D554" s="3" t="inlineStr"/>
       <c r="E554" s="3" t="inlineStr"/>
-      <c r="F554" s="3" t="inlineStr"/>
-      <c r="G554" s="3" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" s="3" t="inlineStr">
@@ -12210,8 +11078,6 @@
       </c>
       <c r="D555" s="3" t="inlineStr"/>
       <c r="E555" s="3" t="inlineStr"/>
-      <c r="F555" s="3" t="inlineStr"/>
-      <c r="G555" s="3" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="3" t="inlineStr">
@@ -12231,8 +11097,6 @@
       </c>
       <c r="D556" s="3" t="inlineStr"/>
       <c r="E556" s="3" t="inlineStr"/>
-      <c r="F556" s="3" t="inlineStr"/>
-      <c r="G556" s="3" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="3" t="inlineStr">
@@ -12252,8 +11116,6 @@
       </c>
       <c r="D557" s="3" t="inlineStr"/>
       <c r="E557" s="3" t="inlineStr"/>
-      <c r="F557" s="3" t="inlineStr"/>
-      <c r="G557" s="3" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="3" t="inlineStr">
@@ -12273,8 +11135,6 @@
       </c>
       <c r="D558" s="3" t="inlineStr"/>
       <c r="E558" s="3" t="inlineStr"/>
-      <c r="F558" s="3" t="inlineStr"/>
-      <c r="G558" s="3" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" s="3" t="inlineStr">
@@ -12294,8 +11154,6 @@
       </c>
       <c r="D559" s="3" t="inlineStr"/>
       <c r="E559" s="3" t="inlineStr"/>
-      <c r="F559" s="3" t="inlineStr"/>
-      <c r="G559" s="3" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="3" t="inlineStr">
@@ -12315,8 +11173,6 @@
       </c>
       <c r="D560" s="3" t="inlineStr"/>
       <c r="E560" s="3" t="inlineStr"/>
-      <c r="F560" s="3" t="inlineStr"/>
-      <c r="G560" s="3" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="3" t="inlineStr">
@@ -12336,8 +11192,6 @@
       </c>
       <c r="D561" s="3" t="inlineStr"/>
       <c r="E561" s="3" t="inlineStr"/>
-      <c r="F561" s="3" t="inlineStr"/>
-      <c r="G561" s="3" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="3" t="inlineStr">
@@ -12357,8 +11211,6 @@
       </c>
       <c r="D562" s="3" t="inlineStr"/>
       <c r="E562" s="3" t="inlineStr"/>
-      <c r="F562" s="3" t="inlineStr"/>
-      <c r="G562" s="3" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="3" t="inlineStr">
@@ -12378,8 +11230,6 @@
       </c>
       <c r="D563" s="3" t="inlineStr"/>
       <c r="E563" s="3" t="inlineStr"/>
-      <c r="F563" s="3" t="inlineStr"/>
-      <c r="G563" s="3" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="3" t="inlineStr">
@@ -12399,8 +11249,6 @@
       </c>
       <c r="D564" s="3" t="inlineStr"/>
       <c r="E564" s="3" t="inlineStr"/>
-      <c r="F564" s="3" t="inlineStr"/>
-      <c r="G564" s="3" t="inlineStr"/>
     </row>
     <row r="565">
       <c r="A565" s="3" t="inlineStr">
@@ -12420,8 +11268,6 @@
       </c>
       <c r="D565" s="3" t="inlineStr"/>
       <c r="E565" s="3" t="inlineStr"/>
-      <c r="F565" s="3" t="inlineStr"/>
-      <c r="G565" s="3" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="3" t="inlineStr">
@@ -12441,8 +11287,6 @@
       </c>
       <c r="D566" s="3" t="inlineStr"/>
       <c r="E566" s="3" t="inlineStr"/>
-      <c r="F566" s="3" t="inlineStr"/>
-      <c r="G566" s="3" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="3" t="inlineStr">
@@ -12462,8 +11306,6 @@
       </c>
       <c r="D567" s="3" t="inlineStr"/>
       <c r="E567" s="3" t="inlineStr"/>
-      <c r="F567" s="3" t="inlineStr"/>
-      <c r="G567" s="3" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="3" t="inlineStr">
@@ -12483,8 +11325,6 @@
       </c>
       <c r="D568" s="3" t="inlineStr"/>
       <c r="E568" s="3" t="inlineStr"/>
-      <c r="F568" s="3" t="inlineStr"/>
-      <c r="G568" s="3" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="3" t="inlineStr">
@@ -12504,8 +11344,6 @@
       </c>
       <c r="D569" s="3" t="inlineStr"/>
       <c r="E569" s="3" t="inlineStr"/>
-      <c r="F569" s="3" t="inlineStr"/>
-      <c r="G569" s="3" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" s="3" t="inlineStr">
@@ -12525,8 +11363,6 @@
       </c>
       <c r="D570" s="3" t="inlineStr"/>
       <c r="E570" s="3" t="inlineStr"/>
-      <c r="F570" s="3" t="inlineStr"/>
-      <c r="G570" s="3" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="3" t="inlineStr">
@@ -12546,8 +11382,6 @@
       </c>
       <c r="D571" s="3" t="inlineStr"/>
       <c r="E571" s="3" t="inlineStr"/>
-      <c r="F571" s="3" t="inlineStr"/>
-      <c r="G571" s="3" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" s="3" t="inlineStr">
@@ -12567,8 +11401,6 @@
       </c>
       <c r="D572" s="3" t="inlineStr"/>
       <c r="E572" s="3" t="inlineStr"/>
-      <c r="F572" s="3" t="inlineStr"/>
-      <c r="G572" s="3" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="3" t="inlineStr">
@@ -12588,8 +11420,6 @@
       </c>
       <c r="D573" s="3" t="inlineStr"/>
       <c r="E573" s="3" t="inlineStr"/>
-      <c r="F573" s="3" t="inlineStr"/>
-      <c r="G573" s="3" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" s="3" t="inlineStr">
@@ -12609,8 +11439,6 @@
       </c>
       <c r="D574" s="3" t="inlineStr"/>
       <c r="E574" s="3" t="inlineStr"/>
-      <c r="F574" s="3" t="inlineStr"/>
-      <c r="G574" s="3" t="inlineStr"/>
     </row>
     <row r="575">
       <c r="A575" s="3" t="inlineStr">
@@ -12630,8 +11458,6 @@
       </c>
       <c r="D575" s="3" t="inlineStr"/>
       <c r="E575" s="3" t="inlineStr"/>
-      <c r="F575" s="3" t="inlineStr"/>
-      <c r="G575" s="3" t="inlineStr"/>
     </row>
     <row r="576">
       <c r="A576" s="3" t="inlineStr">
@@ -12651,8 +11477,6 @@
       </c>
       <c r="D576" s="3" t="inlineStr"/>
       <c r="E576" s="3" t="inlineStr"/>
-      <c r="F576" s="3" t="inlineStr"/>
-      <c r="G576" s="3" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="3" t="inlineStr">
@@ -12672,8 +11496,6 @@
       </c>
       <c r="D577" s="3" t="inlineStr"/>
       <c r="E577" s="3" t="inlineStr"/>
-      <c r="F577" s="3" t="inlineStr"/>
-      <c r="G577" s="3" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="3" t="inlineStr">
@@ -12693,8 +11515,6 @@
       </c>
       <c r="D578" s="3" t="inlineStr"/>
       <c r="E578" s="3" t="inlineStr"/>
-      <c r="F578" s="3" t="inlineStr"/>
-      <c r="G578" s="3" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" s="3" t="inlineStr">
@@ -12714,8 +11534,6 @@
       </c>
       <c r="D579" s="3" t="inlineStr"/>
       <c r="E579" s="3" t="inlineStr"/>
-      <c r="F579" s="3" t="inlineStr"/>
-      <c r="G579" s="3" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" s="3" t="inlineStr">
@@ -12735,8 +11553,6 @@
       </c>
       <c r="D580" s="3" t="inlineStr"/>
       <c r="E580" s="3" t="inlineStr"/>
-      <c r="F580" s="3" t="inlineStr"/>
-      <c r="G580" s="3" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" s="3" t="inlineStr">
@@ -12756,8 +11572,6 @@
       </c>
       <c r="D581" s="3" t="inlineStr"/>
       <c r="E581" s="3" t="inlineStr"/>
-      <c r="F581" s="3" t="inlineStr"/>
-      <c r="G581" s="3" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" s="3" t="inlineStr">
@@ -12777,8 +11591,6 @@
       </c>
       <c r="D582" s="3" t="inlineStr"/>
       <c r="E582" s="3" t="inlineStr"/>
-      <c r="F582" s="3" t="inlineStr"/>
-      <c r="G582" s="3" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" s="3" t="inlineStr">
@@ -12798,8 +11610,6 @@
       </c>
       <c r="D583" s="3" t="inlineStr"/>
       <c r="E583" s="3" t="inlineStr"/>
-      <c r="F583" s="3" t="inlineStr"/>
-      <c r="G583" s="3" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" s="3" t="inlineStr">
@@ -12819,8 +11629,6 @@
       </c>
       <c r="D584" s="3" t="inlineStr"/>
       <c r="E584" s="3" t="inlineStr"/>
-      <c r="F584" s="3" t="inlineStr"/>
-      <c r="G584" s="3" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="3" t="inlineStr">
@@ -12840,8 +11648,6 @@
       </c>
       <c r="D585" s="3" t="inlineStr"/>
       <c r="E585" s="3" t="inlineStr"/>
-      <c r="F585" s="3" t="inlineStr"/>
-      <c r="G585" s="3" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" s="3" t="inlineStr">
@@ -12861,8 +11667,6 @@
       </c>
       <c r="D586" s="3" t="inlineStr"/>
       <c r="E586" s="3" t="inlineStr"/>
-      <c r="F586" s="3" t="inlineStr"/>
-      <c r="G586" s="3" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="3" t="inlineStr">
@@ -12882,8 +11686,6 @@
       </c>
       <c r="D587" s="3" t="inlineStr"/>
       <c r="E587" s="3" t="inlineStr"/>
-      <c r="F587" s="3" t="inlineStr"/>
-      <c r="G587" s="3" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="3" t="inlineStr">
@@ -12903,8 +11705,6 @@
       </c>
       <c r="D588" s="3" t="inlineStr"/>
       <c r="E588" s="3" t="inlineStr"/>
-      <c r="F588" s="3" t="inlineStr"/>
-      <c r="G588" s="3" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="3" t="inlineStr">
@@ -12924,8 +11724,6 @@
       </c>
       <c r="D589" s="3" t="inlineStr"/>
       <c r="E589" s="3" t="inlineStr"/>
-      <c r="F589" s="3" t="inlineStr"/>
-      <c r="G589" s="3" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="3" t="inlineStr">
@@ -12945,8 +11743,6 @@
       </c>
       <c r="D590" s="3" t="inlineStr"/>
       <c r="E590" s="3" t="inlineStr"/>
-      <c r="F590" s="3" t="inlineStr"/>
-      <c r="G590" s="3" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="3" t="inlineStr">
@@ -12966,8 +11762,6 @@
       </c>
       <c r="D591" s="3" t="inlineStr"/>
       <c r="E591" s="3" t="inlineStr"/>
-      <c r="F591" s="3" t="inlineStr"/>
-      <c r="G591" s="3" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="3" t="inlineStr">
@@ -12987,8 +11781,6 @@
       </c>
       <c r="D592" s="3" t="inlineStr"/>
       <c r="E592" s="3" t="inlineStr"/>
-      <c r="F592" s="3" t="inlineStr"/>
-      <c r="G592" s="3" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="3" t="inlineStr">
@@ -13008,8 +11800,6 @@
       </c>
       <c r="D593" s="3" t="inlineStr"/>
       <c r="E593" s="3" t="inlineStr"/>
-      <c r="F593" s="3" t="inlineStr"/>
-      <c r="G593" s="3" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="3" t="inlineStr">
@@ -13029,8 +11819,6 @@
       </c>
       <c r="D594" s="3" t="inlineStr"/>
       <c r="E594" s="3" t="inlineStr"/>
-      <c r="F594" s="3" t="inlineStr"/>
-      <c r="G594" s="3" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="3" t="inlineStr">
@@ -13050,8 +11838,6 @@
       </c>
       <c r="D595" s="3" t="inlineStr"/>
       <c r="E595" s="3" t="inlineStr"/>
-      <c r="F595" s="3" t="inlineStr"/>
-      <c r="G595" s="3" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="3" t="inlineStr">
@@ -13071,8 +11857,6 @@
       </c>
       <c r="D596" s="3" t="inlineStr"/>
       <c r="E596" s="3" t="inlineStr"/>
-      <c r="F596" s="3" t="inlineStr"/>
-      <c r="G596" s="3" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="3" t="inlineStr">
@@ -13092,8 +11876,6 @@
       </c>
       <c r="D597" s="3" t="inlineStr"/>
       <c r="E597" s="3" t="inlineStr"/>
-      <c r="F597" s="3" t="inlineStr"/>
-      <c r="G597" s="3" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="3" t="inlineStr">
@@ -13113,8 +11895,6 @@
       </c>
       <c r="D598" s="3" t="inlineStr"/>
       <c r="E598" s="3" t="inlineStr"/>
-      <c r="F598" s="3" t="inlineStr"/>
-      <c r="G598" s="3" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="3" t="inlineStr">
@@ -13134,8 +11914,6 @@
       </c>
       <c r="D599" s="3" t="inlineStr"/>
       <c r="E599" s="3" t="inlineStr"/>
-      <c r="F599" s="3" t="inlineStr"/>
-      <c r="G599" s="3" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="3" t="inlineStr">
@@ -13155,8 +11933,6 @@
       </c>
       <c r="D600" s="3" t="inlineStr"/>
       <c r="E600" s="3" t="inlineStr"/>
-      <c r="F600" s="3" t="inlineStr"/>
-      <c r="G600" s="3" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="3" t="inlineStr">
@@ -13176,8 +11952,6 @@
       </c>
       <c r="D601" s="3" t="inlineStr"/>
       <c r="E601" s="3" t="inlineStr"/>
-      <c r="F601" s="3" t="inlineStr"/>
-      <c r="G601" s="3" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="3" t="inlineStr">
@@ -13197,8 +11971,6 @@
       </c>
       <c r="D602" s="3" t="inlineStr"/>
       <c r="E602" s="3" t="inlineStr"/>
-      <c r="F602" s="3" t="inlineStr"/>
-      <c r="G602" s="3" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="3" t="inlineStr">
@@ -13218,8 +11990,6 @@
       </c>
       <c r="D603" s="3" t="inlineStr"/>
       <c r="E603" s="3" t="inlineStr"/>
-      <c r="F603" s="3" t="inlineStr"/>
-      <c r="G603" s="3" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" s="3" t="inlineStr">
@@ -13239,8 +12009,6 @@
       </c>
       <c r="D604" s="3" t="inlineStr"/>
       <c r="E604" s="3" t="inlineStr"/>
-      <c r="F604" s="3" t="inlineStr"/>
-      <c r="G604" s="3" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="3" t="inlineStr">
@@ -13260,8 +12028,6 @@
       </c>
       <c r="D605" s="3" t="inlineStr"/>
       <c r="E605" s="3" t="inlineStr"/>
-      <c r="F605" s="3" t="inlineStr"/>
-      <c r="G605" s="3" t="inlineStr"/>
     </row>
     <row r="606">
       <c r="A606" s="3" t="inlineStr">
@@ -13281,8 +12047,6 @@
       </c>
       <c r="D606" s="3" t="inlineStr"/>
       <c r="E606" s="3" t="inlineStr"/>
-      <c r="F606" s="3" t="inlineStr"/>
-      <c r="G606" s="3" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="3" t="inlineStr">
@@ -13302,8 +12066,6 @@
       </c>
       <c r="D607" s="3" t="inlineStr"/>
       <c r="E607" s="3" t="inlineStr"/>
-      <c r="F607" s="3" t="inlineStr"/>
-      <c r="G607" s="3" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="3" t="inlineStr">
@@ -13323,8 +12085,6 @@
       </c>
       <c r="D608" s="3" t="inlineStr"/>
       <c r="E608" s="3" t="inlineStr"/>
-      <c r="F608" s="3" t="inlineStr"/>
-      <c r="G608" s="3" t="inlineStr"/>
     </row>
     <row r="609">
       <c r="A609" s="3" t="inlineStr">
@@ -13344,8 +12104,6 @@
       </c>
       <c r="D609" s="3" t="inlineStr"/>
       <c r="E609" s="3" t="inlineStr"/>
-      <c r="F609" s="3" t="inlineStr"/>
-      <c r="G609" s="3" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="3" t="inlineStr">
@@ -13365,8 +12123,6 @@
       </c>
       <c r="D610" s="3" t="inlineStr"/>
       <c r="E610" s="3" t="inlineStr"/>
-      <c r="F610" s="3" t="inlineStr"/>
-      <c r="G610" s="3" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="3" t="inlineStr">
@@ -13386,8 +12142,6 @@
       </c>
       <c r="D611" s="3" t="inlineStr"/>
       <c r="E611" s="3" t="inlineStr"/>
-      <c r="F611" s="3" t="inlineStr"/>
-      <c r="G611" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
